--- a/characteristics_tables/Influenza_Study_Characteristics.xlsx
+++ b/characteristics_tables/Influenza_Study_Characteristics.xlsx
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10 866</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Critical: D1: Confounding</t>
+          <t>Critical: D1: Confounding; assessment in progress</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5903,11 +5903,6 @@
       <c r="T59" t="inlineStr">
         <is>
           <t>https://doi.org/10.1056/NEJMoa2516491</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Some Concerns: D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
@@ -10618,7 +10613,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10641,7 +10636,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11129,7 +11124,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>10866</v>
       </c>
     </row>
     <row r="14">
@@ -11781,7 +11776,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D54">
@@ -14369,7 +14364,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16309,7 +16304,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -16703,7 +16698,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E519"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -22959,60 +22954,50 @@
     </row>
     <row r="290">
       <c r="A290">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B290">
-        <v>1960</v>
+        <v>1924</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SalamancadelaCueva 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B291">
-        <v>1969</v>
+        <v>1924</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Jain 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B292">
-        <v>1969</v>
+        <v>1960</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jain 2025</t>
+          <t>SalamancadelaCueva 2025</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -23051,14 +23036,14 @@
     </row>
     <row r="294">
       <c r="A294">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B294">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Jain 2025</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -23074,14 +23059,14 @@
     </row>
     <row r="295">
       <c r="A295">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B295">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Jain 2025</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -23120,14 +23105,14 @@
     </row>
     <row r="297">
       <c r="A297">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B297">
-        <v>2150</v>
+        <v>1970</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -23143,14 +23128,14 @@
     </row>
     <row r="298">
       <c r="A298">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B298">
-        <v>2150</v>
+        <v>1970</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -23396,14 +23381,14 @@
     </row>
     <row r="309">
       <c r="A309">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B309">
-        <v>2420</v>
+        <v>2150</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -23419,14 +23404,14 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B310">
-        <v>2420</v>
+        <v>2150</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -23695,83 +23680,93 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B322">
-        <v>2680</v>
+        <v>2420</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Folegatti 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B323">
-        <v>2680</v>
+        <v>2420</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Folegatti 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B324">
-        <v>3183</v>
+        <v>2680</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Folegatti 2026</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B325">
-        <v>3183</v>
+        <v>2680</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Folegatti 2026</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
@@ -24659,14 +24654,14 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B375">
-        <v>3947</v>
+        <v>3183</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Maloney 2026</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -24677,14 +24672,14 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B376">
-        <v>3947</v>
+        <v>3183</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Maloney 2026</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -25001,47 +24996,37 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B394">
-        <v>4110</v>
+        <v>3947</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B395">
-        <v>4110</v>
+        <v>3947</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
@@ -25082,25 +25067,25 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B398">
-        <v>4748</v>
+        <v>4110</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Comstock 2026</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -25116,24 +25101,24 @@
     </row>
     <row r="399">
       <c r="A399">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B399">
-        <v>4748</v>
+        <v>4110</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Comstock 2026</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>D1: Randomization</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
@@ -25289,25 +25274,25 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B407">
-        <v>5196</v>
+        <v>4748</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Bonduelle 2025</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -25323,60 +25308,70 @@
     </row>
     <row r="408">
       <c r="A408">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B408">
-        <v>5422</v>
+        <v>4748</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Chime 2025</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>D1: Randomization</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B409">
-        <v>5751</v>
+        <v>5196</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Bonduelle 2025</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B410">
-        <v>5751</v>
+        <v>5422</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Chime 2025</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
@@ -25814,290 +25809,250 @@
     </row>
     <row r="435">
       <c r="A435">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B435">
-        <v>5810</v>
+        <v>5751</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B436">
-        <v>5810</v>
+        <v>5751</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B437">
-        <v>5810</v>
+        <v>5814</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B438">
-        <v>5810</v>
+        <v>5814</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B439">
-        <v>5810</v>
+        <v>5814</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B440">
-        <v>5810</v>
+        <v>5814</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="B441">
-        <v>5810</v>
+        <v>21829</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Rezahosseini 2026</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442">
-        <v>141</v>
+        <v>268</v>
       </c>
       <c r="B442">
-        <v>5810</v>
+        <v>32935</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026 (NEW)</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="B443">
-        <v>5814</v>
+        <v>32935</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="B444">
-        <v>5814</v>
+        <v>32935</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="B445">
-        <v>5814</v>
+        <v>32935</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="B446">
-        <v>5814</v>
+        <v>32935</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>assessment in progress</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c r="B447">
-        <v>21829</v>
+        <v>32935</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Rezahosseini 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -27289,114 +27244,6 @@
         </is>
       </c>
       <c r="D513" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514">
-        <v>268</v>
-      </c>
-      <c r="B514">
-        <v>32935</v>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515">
-        <v>268</v>
-      </c>
-      <c r="B515">
-        <v>32935</v>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516">
-        <v>268</v>
-      </c>
-      <c r="B516">
-        <v>32935</v>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517">
-        <v>268</v>
-      </c>
-      <c r="B517">
-        <v>32935</v>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518">
-        <v>268</v>
-      </c>
-      <c r="B518">
-        <v>32935</v>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519">
-        <v>268</v>
-      </c>
-      <c r="B519">
-        <v>32935</v>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
         <is>
           <t>assessment in progress</t>
         </is>

--- a/characteristics_tables/Influenza_Study_Characteristics.xlsx
+++ b/characteristics_tables/Influenza_Study_Characteristics.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U76"/>
+  <dimension ref="A1:Z76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -393,75 +393,100 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Study Period Start</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Study Period End</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Total N</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Study Design</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Study Design Specifics</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Virus</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Country/Region</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Setting Details</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Vaccine Products</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Outcomes Reported (Characteristics Consensus)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Outcomes Reported</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Domains Reported</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Funding Source</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PMID</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>PMCID</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Risk of Bias (Detailed)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Risk of Bias</t>
         </is>
@@ -496,57 +521,82 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>18476</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>United States, South Africa, and the Philippines</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Life-threatening short-term reactions, Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Life-threatening short-term reactions, Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Funded by Pfizer</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>New England Journal of Medicine</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1056/NEJMoa2416779</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Low; assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Low; Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -579,72 +629,97 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>15448</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Other local or regional database: electronic medical record (EMR) data from the Military Health System (MHS) Data Repository (MDR)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Symptom severity/duration, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Symptom severity/duration, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Federal funds from the Defense Health Program (US Department of Defense) and Defense Health Agency Immunization Healthcare Division, under award HU0001190002, the Defense Health Agency Armed Forces Health Surveillance Division Global Emerging Infections Surveillance Branch (ProMIS ID P0014_18_US and P0007_19_US), and from the National Institute of Allergy and Infectious Diseases, National Institutes of Health (NIH), under Inter-Agency Agreement Y1-Al-5072. This project has also been funded in part with federal funds from the National Institutes of Health Clinical Center and the National Cancer Institute, National Institutes of Health, under Contract No. 75N91019D00024 Task Order No. 75N91019F00130</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Clinical Infectious Diseases</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>40973113</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>PMC12728286</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12728286/</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/cid/ciaf503</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>High: D1: Randomization; Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>High; Some Concerns</t>
         </is>
       </c>
     </row>
@@ -670,79 +745,89 @@
           <t>Adults, Pregnant</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>RCT</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>H1N1 monovalent (2009)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>This work was supported, in part, by NIH/NIAID award U19AI145825. DMID Clinical Study 09-0072 was supported by contract number N01AI80057C</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>can Society for Microbiology</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>41332801</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>PMC12668064</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13059737/</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>https://doi.org/10.1101/2025.11.18.25340497</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -775,57 +860,82 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>43086</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Other US postmarketing registry: Veradigm Integrated Dataset</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>CSL Seqirus.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Influenza and other Respiratory Viruses</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/irv.70180</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Serious: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -858,67 +968,92 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>542</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Canadian Hutterite Colonies (secondary analysis)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>aIIV4</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Journal of Clinical Virology Plus</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S266703802500033X?via%3Dihub</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jcvp.2025.100234</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Serious: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -952,72 +1087,97 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>850</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prespecified analysis of DANFLU-1 trial</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>Sanofi (Lyon, France), who provided HD-IIV and a financial contribution. Trial sponsor: Copenhagen University Hospital - Herlev and Gentofte.</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Respiratory Investigation</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>41177098</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S2212534525001753?via%3Dihub</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.resinv.2025.10.016</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>High: D1: Randomization; Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>High; Some Concerns</t>
         </is>
       </c>
     </row>
@@ -1050,72 +1210,97 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>4906905</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Other OUS postmarketing registry: Immunization Information System (CNAEFIS) and Jiangsu Provincial Electronic Immunization Registries System (JSEIRS) systems.</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>IIV3, IIV4</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Safety: Guillain-Barre syndrome, Febrile seizure, Life-threatening short-term reactions</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Safety: Guillain-Barré syndrome, Febrile seizure, Life-threatening short-term reactions</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Scientific Research Project of the Jiangsu Provincial Health Commission (M2021030, R.H.) and the Research Project of Nanjing Medical University (NMUB20220014, PL).</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Vaccines (Basel)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>41295527</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>PMC12656768</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12656768/</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/vaccines13111154</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1148,62 +1333,87 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>214075</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>case-control: test‑negative design</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Other local or regional database: NHS, Respiratory DataMart, Second-Generation Surveillance System, Secondary Uses Service, The Immunisation Information System,</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>LAIV4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>UK Health Security Agency.</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Influenza and other Respiratory Viruses</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/irv.70194</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -1236,57 +1446,82 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>348958</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>RSV, COVID, Influenza</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Kaiser Permanente (any/multiple)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>LAIV4</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence, Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>The Center for Forecasting and Outbreak Analytics of the US Centers for Disease Control &amp; Prevention via the Insight Net cooperative agreement (CDC-RFA-FT-23-0069 to SYT and JAL). The funders had no role in study design, data collection and analysis, decision to publish, or preparation of the manuscript.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>PLoS Comput Biol</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>https://doi.org/10.1371/journal.pcbi.1013723</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1319,70 +1554,95 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>19917</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>case-control: test‑negative design</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Other local or regional database: 7 US pediatric medical centers within US New Vaccine Surveillance Network (NVSN)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>US CDC</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Pediatrics</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>41936402</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/41936402/</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>https://doi.org/10.1542/peds.2025-073973</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
@@ -1415,70 +1675,95 @@
           <t>01/2019 - 10/2023</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Other local or regional database: Department of Homeland Security through the Freedom of Information Act for 8 communicable diseases over 1 decade (filed October 2023) from available facilities. We collected weekly national influenza hospital visit counts from the Centers for Disease Control and Prevention FluView database.
 Deidentified, individual-level data.</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>JAMA Network</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>41123889</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>PMC12547590</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12547590/</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1001/jamanetworkopen.2025.44278</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1511,72 +1796,97 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>33343</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Other US postmarketing registry: US Influenza Vaccine Effectiveness (Flu VE) Network</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>M. G., E. T. M., A. S. M., R. K. Z., M. P. N., E. K., C. H. P., H. Q. N., report institutional cooperative agreement grant funding from the Centers for Disease Control and Prevention (CDC), and R. K. Z. and M. P. N. report institutional funding from the National Institutes of Health. M. G. reports support from CDC-Vanderbilt University Medical Center, CDC-Westat, and CDC-Abt Associates for other studies and a speaker panel honorarium from the Texas Pediatric Society, sponsored by the American Academy of Pediatrics and CDC Project Firstline. A. S. M. reports institutional funding from the National Institute of Allergy and Infectious Diseases for other studies. R. K. Z. reports institutional funds from Sanofi Pasteur for other studies. M. P. N. reports institutional funding from Astra Zeneca, Sanofi, and Merck Sharp &amp; Dohme for other studies and consulting fees from GSK and Merck. H. Q. N. reports institutional funding for other unrelated studies from GSK, Moderna, and Seqirus and participation on a scientific advisory board for Seqirus and Moderna. J. P. K. reports institutional research support from GSK and Moderna for other studies</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Clinical Infectious Diseases</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>41102880</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>PMC12667161</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12667161/</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/cid/ciaf579</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -1609,60 +1919,80 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>10866</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>RSV, Influenza</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Colorado Hospital Association (CHA) database</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>RSV vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>AstraZeneca United States</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>The Journal of Infectious Diseases</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>40690544</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/40690544/</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/infdis/jiaf381</t>
         </is>
@@ -1697,62 +2027,87 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>29932</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>CANVAS</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>IIV3, aIIV4</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Safety: Febrile seizure, Reactogenicity limiting activities of daily living (e.g., SIRVA), Life-threatening short-term reactions</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Safety: Febrile seizure, Reactogenicity limiting activities of daily living (e.g., SIRVA), Life-threatening short-term reactions</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>The Canadian National Vaccine Safety Network as part of the Canadian Immunization Research Network is funded by the Canadian Institutes of Health Research and the Public Health Agency of Canada grant #151944.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S2590136225001056?via%3Dihub</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jvacx.2025.100711</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding; Serious: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Critical; Serious</t>
         </is>
       </c>
     </row>
@@ -1786,73 +2141,98 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>1056</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>multicenter, randomized, open-label, uncontrolled study</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>CSL Seqirus;</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t xml:space="preserve">Vaccines (Basel)_x000D_
 </t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>41150407</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>PMC12568138</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12568138/</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/vaccines13101019</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Critical: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1885,74 +2265,99 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>1801,
 Had previous stroke: 67,
 Did not have previous stroke: 1734</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>subanalysis</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Other local or regional database: across 25 centers in Brazil</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits; Safety: Myocardial infarction, Stroke (ischemic, hemorrhagic)</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits; Safety: Myocardial infarction, Stroke (ischemic, hemorrhagic)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Brazilian Ministry of Health. PROADISUS (grant numbers NUP-25000.030761/2018-54 and NUP- 25000.000209/2021-37)</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>International Journal of Stroke</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>40973981</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/40973981/</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/17474930251383626</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>High: D1: Randomization; Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>High; Some Concerns</t>
         </is>
       </c>
     </row>
@@ -1985,67 +2390,92 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>73132720</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Influenza-Associated Pediatric Mortality Surveillance System</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-specific mortality</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>MMWR. Morbidity and mortality weekly report</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>40996933</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>PMC12463192</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12463192/</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>https://doi.org/10.15585/mmwr.mm7436a2</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2078,67 +2508,92 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Other local or regional database: FluSurv-NET | FluView, New Vaccine Surveillance Network | NVSN, and Influenza-Associated Pediatric Mortality | CDC</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>MMWR. Morbidity and mortality weekly report</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>40996921</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>PMC12463191</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12463191/</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://doi.org/10.15585/mmwr.mm7436a1</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2171,67 +2626,92 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>9973703</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Administrative claims from commercial insurance databases: CVS Health, Carelon Research, and Optum</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Safety: Guillain-Barre syndrome, Stroke (ischemic, hemorrhagic), Febrile seizure, Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Safety: Guillain-Barré syndrome, Febrile seizure, Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>The U.S. Food and Drug Administration through the Department of Health and Human Services (HHS) Contract HHSF-223-2018-10020I and Task Order 75F40123F19005.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>40845790</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/40845790/</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.vaccine.2025.127614</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2262,69 +2742,94 @@
           <t>10/2024 - 04/2025</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Emerging Infections Program Network</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>CDC Emerging Infections Program cooperative agreement. Council of State and Territorial Epidemiologists (CSTE) grants. Goldbelt Professional Services contract</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Morbidity and Mortality Weekly Report (MMWR)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>40934142</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>PMC12425177</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>https://www.cdc.gov/mmwr/volumes/74/wr/mm7434a1.htm</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>https://doi.org/10.15585/mmwr.mm7434a1</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2361,72 +2866,97 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>1499</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Australia, Costa Rica, Honduras and the Philippines</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>CSL under a collaboration agreement with Arcturus Therapeutics.</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>eClinicalMedicine</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>40896462</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>PMC12396474</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12396474/</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.eclinm.2025.103428</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Critical: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2459,67 +2989,92 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>RIV4</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Sanofi.</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>40752250</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0264410X25008187?via%3Dihub</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.vaccine.2025.127521</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Some Concerns</t>
         </is>
       </c>
     </row>
@@ -2552,72 +3107,97 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>245498</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Kaiser Permanente (any/multiple)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Grants No. 5R01AI168373-03 and K01AI139275 from the National Institute of Allergy and Infectious Disease</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>Obstetrics &amp; Gynecology</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>40570349</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>PMC12270756</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/40570349/</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/AOG.0000000000005986</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2650,67 +3230,92 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>1617 neighborhoods</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Other local or regional database: New York State Health Care Utilization Project, State Inpatient Databases (SID); encounter-level administrative claims dataset (AHRQ); covers all payers (Medicaid, Medicare, commercial, uninsured); zip code tabulation areas (ZCTAs) used as neighborhood proxy; 2009-2013 5-year American Community Survey (ACS) ZCTA data for neighborhood-level variables.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>National Institute of Allergy and Infectious Diseases (grant K01AI168579-03 to A. S. M.).</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Open Forum Infectious Diseases</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>40874190</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>PMC12378228</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12378228/</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/ofid/ofaf468</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2738,78 +3343,103 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pfizer/Moderna COVID - 12/2020 - 01/2022
+          <t>Pfizer/Moderna COVID - 19 vaccine: 12/2020 - 01/2022; 
 Influenza vaccine: 01/2016 - 01/2022</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>40650</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Influenza, COVID</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Other local or regional database: electronic health records (EHR) data from Stanford Health Care (SHC)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA)</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA)</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>The T32DC015209 training grant from the National Institute on Deafness and Other Communication Disorders (TM), the Remondi Foundation (KMS), and the Bertarelli Foundation Endowed Professorship (KMS).</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>Frontiers in Neurology</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>40852523</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>PMC12367506</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12367506/</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>https://doi.org/10.3389/fneur.2025.1637870</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -2842,72 +3472,97 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>15458</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>VAERS</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>IIV4, LAIV4</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Safety: Guillain-Barré syndrome, Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>Frontiers in Pediatrics</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>40963961</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>PMC12436442</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>https://www.frontiersin.org/journals/pediatrics/articles/10.3389/fped.2025.1640498/full</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>https://doi.org/10.3389/fped.2025.1640498</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2940,72 +3595,97 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>6506</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>COVID, Influenza</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>CANVAS</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>IIV4, aIIV4, LAIV4, HD-IIV4, Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA)</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>The CANVAS-COVID study was supported by the COVID-19 Vaccine Readiness funding from the Canadian Institutes of Health Research and the Public Health Agency of Canada CANVAS grant number CVV-450980. It was also supported by funding from the Public Health Agency of Canada, through the Vaccine Surveillance Reference group and the COVID-19 Immunity Task Force.</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>Human Vaccines and Immunotherapeutics</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>40963477</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>PMC12452431</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12452431/</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/21645515.2025.2560172</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding; assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Critical; Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -3038,57 +3718,82 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Belgium, Germany, Spain</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>GSK safety monitoring (BE, DE, ES)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>GSK [study identifier: 214775]</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>Human Vaccines and Immunotherapeutics</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/21645515.2025.2569735</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3121,57 +3826,82 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>GSK [study number: 218702]. All authors were involved in study conception and design, data analysis, data interpretation, and the decision to submit the article for publication. GSK funded the article processing charges and open-access fee.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Human Vaccines and Immunotherapeutics</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/21645515.2025.2578084</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3204,57 +3934,82 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>1249</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Influenza, COVID, RSV</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>VAERS</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>RSV vaccine (unspecified), COVID-19 vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>Frontiers in Pharmacology</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>https://doi.org/10.3389/fphar.2025.1682119</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3287,57 +4042,82 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>RIV4</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>The study was funded by a grant from the French Ministry of Health (PHRC-N 2019). Sanofi provided the vaccines used during the study, and Sanofi laboratory (Global Clinical Immunology Platform) in Swiftwater, Pennsylvania, United States, did the testing. Sanofi had no role in the study design, data analysis, publication decision, or manuscript preparation.</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>Clinical infectious diseases : an official publication of the Infectious Diseases Society of America</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/cid/ciag200</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Critical: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3370,77 +4150,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>466320</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Denmark, Spain</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Other local or regional database: Both trials leveraged passively collected health data sourced from Danish and Galician administrative health registries</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>HD-IIV4</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>Sanofi</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>Circulation</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>41212981</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>PMC12991342</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12991342/</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>https://doi.org/10.1161/CIRCULATIONAHA.125.077801</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3473,67 +4278,92 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>1993</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Other local or regional database: Hospitalized Adult Influenza Vaccine Effectiveness Network (HAIVEN)</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>E. T. M. reports receiving research funding from Merck. A. S. M. reports receiving research funding from the National Institute of Allergy and Infectious Diseases. R. K. Z. reports receiving research funding from the National Institutes of Health (UL1TR001857) and Sanofi Pasteur</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>Clinical Infectious Diseases</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>41004324</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>PMC12817258</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12817258/</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/cid/ciaf545</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3566,72 +4396,97 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>835987</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>RSV, COVID, Influenza</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Other US postmarketing registry: VA COVID-19 Shared Data Resource and the Corporate Data Warehouse (CDW)</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Vaccinated (Hepatitis A; MenC; other)</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence, Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>The VA Boston Cooperative Studies Program</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>Frontiers in Public Health</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>42100533</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>PMC13144013</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13144013/</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>https://doi.org/10.3389/fpubh.2026.1808528_x000D_</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3664,72 +4519,97 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>COVID, Influenza</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Danish National Cohort Study of Effectiveness and Safety of SAR-CoV-2 Vaccines (ENFORCE)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>mRNA-1273, BNT162b2</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>Independent Research Fund Denmark (Inge Lehmanns grant number 3162-00031B).</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>Clin Infect Dis.</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>40826247</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>PMC13016764</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>https://academic.oup.com/cid/article/82/2/e343/8237652?login=false</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/cid/ciaf455</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -3762,67 +4642,92 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Other local or regional database: Our influenza surveillance system consists of influenza-like illness (ILI) reporting by sentinel sites; electronic laboratory reporting of influenza-positive polymerase chain reaction tests; influenza-associated hospitalizations connected with emergency department (ED) visits; and testing of samples submitted by hospital laboratories for influenza subtyping, identification of other circulating respiratory viruses, and antiviral resistance screening. Beginning in the period 2020-2021, this surveillance was incorporated into year-round viral respiratory illness surveillance focused on Covid-19, influenza, and respiratory syncytial virus (RSV). Vaccine administration data reported to the Immunization Information Systems are used to calculate coverage.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>NEJM Evidence</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>41544149</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>https://evidence.nejm.org/doi/10.1056/EVIDpha2500136?url_ver=Z39.88-2003&amp;rfr_id=ori:rid:crossref.org&amp;rfr_dat=cr_pub%20%200pubmed</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>https://doi.org/10.1056/EVIDpha2500136</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3855,62 +4760,87 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>366</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>USA, Poland, Spain</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>RIV4</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>Sanofi</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0264410X26003907?via%3Dihub</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.vaccine.2026.128582</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Some Concerns</t>
         </is>
       </c>
     </row>
@@ -3943,57 +4873,82 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>17203</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>The IVY Network</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>(CDC) and coordinated through Vanderbilt University Medical Center (VUMC)</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>PMID: 41518970.</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.vaccine.2025.128192</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Moderate: D3: Selection of participants</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -4026,72 +4981,97 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>142494</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Other US postmarketing registry: 1) The New Vaccine Surveillance Network (NVSN), 2) the U.S. Flu VE Network (U.S. Flu VE), and 3) the Virtual SARS-CoV-2, Influenza, and Other respiratory viruses Network (VISION).</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>Morbidity and Mortality Weekly Report</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>41818161</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>PMC12981535</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12981535/</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>https://doi.org/10.15585/mmwr.mm7509a2</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -4124,25 +5104,35 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>44132 births</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Other local or regional database: EHRs.
 "electronic health records (EHR) from mother-infant pairs" from University of Pittsburgh Medical Center (UPMC); "Pennsylvania Statewide Immunization Information System (PA-SIIS)" for vaccination verification. 
@@ -4150,49 +5140,64 @@
 Methods, Exposure paragraph: "Maternal influenza vaccination was assessed using EHR data and the Pennsylvania Statewide Immunization Information System (PA-SIIS) which verified administration date, lot, and vaccine type."</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Pregnancy-specific safety: Preterm birth, Small for gestational age</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Pregnancy-specific safety: Preterm birth, Small for gestational age</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Pregnancy-specific safety</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>NIH</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>The Pediatric Infectious Disease Journal</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>41736203</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>PMC13094747</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>https://journals.lww.com/pidj/abstract/9900/the_impact_of_maternal_influenza_infection_and.1655.aspx</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/INF.0000000000005194</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Serious: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -4225,62 +5230,87 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>1086</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>case-cohort</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Other US postmarketing registry: US Influenza-Associated Pediatric Mortality Surveillance System - a national, notifiable-condition surveillance system</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-specific mortality</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-specific mortality</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>Pediatrics</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>https://publications.aap.org/pediatrics/article-abstract/doi/10.1542/peds.2026-076453/208191/Influenza-Vaccine-Effectiveness-Against-Pediatric?redirectedFrom=fulltext</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>https://doi.org/10.1542/peds.2026-076453</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4313,72 +5343,97 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>2518329</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>COVID, Influenza</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Other US postmarketing registry: Electronic health records from US Department of Veterans Affairs; VA Corporate Data Warehouse (CDW); VA Health Information Exchange, the CDC Immunization Gateway, state immunization information systems; and other health information exchanges.</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Vaccinated (Hepatitis A; MenC; other)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Safety: Myocarditis/pericarditis (COVID), Myocardial infarction, Guillain-Barre syndrome, Immune thrombocytopenic purpura (ITP) (COVID), Stroke (ischemic, hemorrhagic), Thrombosis (e.g., CVST), Life-threatening short-term reactions</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Safety: Myocarditis/pericarditis (COVID), Myocardial infarction, Guillain-Barré syndrome, Immune thrombocytopenic purpura (ITP) (COVID), Stroke (ischemic, hemorrhagic), Thrombosis (e.g., CVST), Life-threatening short-term reactions</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>U.S. Department of Veterans Affairs.</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>Annals of Internal Medicine</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>42372273</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>https://www.acpjournals.org/doi/10.7326/ANNALS-26-00217-PS?url_ver=Z39.88-2003&amp;rfr_id=ori:rid:crossref.org&amp;rfr_dat=cr_pub%20%200pubmed</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>https://doi.org/10.7326/ANNALS-26-00217-PS</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -4411,67 +5466,92 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>RSV, Influenza</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>ED discharge data from New York State were obtained from the State Inpatient Databases and State Emergency Department Databases of the Healthcare Cost and Utilization Project (HCUP)</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>Supported in part by the National Institutes of Health (NIH) grant number R01AI137093.</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>BMC Infect Dis</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>41606523</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>PMC12924248</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>https://link.springer.com/article/10.1186/s12879-026-12574-6#citeas</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>https://doi.org/10.1186/s12879-026-12574-6</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4504,65 +5584,90 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>5629</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>IIV3</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>CIHR and Seqirus</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>41389704</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/41389704/</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.vaccine.2025.128102</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
         <is>
           <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
@@ -4597,72 +5702,97 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>952765</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Other local or regional database: California Department of Public Health (CDPH)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease, Infection: Disease-specific mortality</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>Morbidity and Mortality Weekly Report</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>41818142</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>PMC13211850</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13211850/</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>https://doi.org/10.15585/mmwr.mm7509a3</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -4695,73 +5825,98 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Influenza, RSV</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>HD-IIV4, mRNA-1345</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
         <is>
           <t>Moderna, Inc.</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>Human vaccines &amp; Immunotherapeutics</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>42048601</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>PMC13128023</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13128023/</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t xml:space="preserve">https://doi.org/10.1080/21645515.2026.2649335
 </t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>High: D1: Randomization; Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>High; Some Concerns</t>
         </is>
       </c>
     </row>
@@ -4789,77 +5944,102 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10/2023 - 07/2024</t>
+          <t>24 October 2023 - 26 July 2024</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>957</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Belgium, Canada, Poland, and the United State</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>HD-IIV3, HD-IIV4</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
         <is>
           <t>Johnson &amp; Johnson and Sanofi.</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>Vaccines (Basel)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>41746067</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>PMC12944986</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12944986/</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/vaccines14020146</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Critical: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4892,77 +6072,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>15875</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>case-control: test‑negative design</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Other local or regional database: New Vaccine Surveillance Network (NVSN) acute respiratory illness (ARI) surveillance data</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Disease-related ICU or NICU admission, Infection: Lab-confirmed disease, Infection: Disease-specific mortality</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Disease-related ICU or NICU admission, Infection: Disease-specific mortality</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>US CDC</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>Pediatrics</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>41506521</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>PMC13027338</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13027338/</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>https://doi.org/10.1542/peds.2025-072184</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding; Moderate: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Critical; Moderate</t>
         </is>
       </c>
     </row>
@@ -4995,72 +6200,97 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>Mahidol University. This study was supported by the Faculty of Medicine Ramathibodi Hospital (RF_64085) and Mahidol University (2564).</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>Clinical and Experimental Medicine</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>40205278</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>PMC11982163</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/40205278/</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s10238-025-01639-6</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>High: D1: Randomization; Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>High; Some Concerns</t>
         </is>
       </c>
     </row>
@@ -5093,67 +6323,92 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Data from the Defense Medical Surveillance System (DMSS) and standardized laboratory data provided by the Defense Centers for Public Health-Portsmouth were utilized for the analysis</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
         <is>
           <t>Medical Surveillance Monthly Report (MSMR)</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>41505694</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>PMC12874399</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12874399/</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>No DOI</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5186,72 +6441,97 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>Sanofi and Centre Hospitalier Annecy Genevois (CHANGE)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>JCI Insight</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>40036077</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>PMC12016920</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12016920/</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>https://doi.org/10.1172/jci.insight.184128</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>High: D1: Randomization</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5284,55 +6564,80 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>2329372</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Denmark, Finland, and Sweden</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Other local or regional database: "In the three countries, we linked demography and healthcare data across different nationwide registries by using the country-specific unique identifiers assigned to all residents. We retrieved individual-level information on brand-specific influenza vaccinations, hospital admissions and recorded disease diagnoses, laboratory-confirmed influenza infections, and demographic (age, sex, and vital status) variables (Supplementary Tables S1 and S2)."</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease, Infection: Disease-specific mortality</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease, Infection: Disease-specific mortality</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
         <is>
           <t>European Medicines Agency.</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>The Lancet Regional Health - Europe</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.lanepe.2025.101518</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
         <is>
           <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
@@ -5367,60 +6672,80 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>287661</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Information Management Technical Advisory Subdirectorate of the Andalusian Health Service</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>The Journal of Pediatrics</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>40122278</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/40122278/</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jpeds.2025.114558</t>
         </is>
@@ -5450,77 +6775,102 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>09/2021 - 06/2022</t>
+          <t>15 September 2021 - 6 June 2022</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>1539</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Canada, Finland, Spain, USA, and Republic of Korea</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>IIV4, aIIV4</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
         <is>
           <t>GSK</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>The Journal of Infectious Diseases</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>38970327</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>PMC11793055</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11793055/</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/infdis/jiae342</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>High: D1: Randomization</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5559,72 +6909,97 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>436</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>Pfizer Inc.</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>Vaccines (Basel)</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>40333267</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>PMC12031420</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12031420/</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/vaccines13040383</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Critical: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5653,77 +7028,102 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10/2024 - 05/2025</t>
+          <t>October 1, 2024 - May 31, 2025</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>1106628</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Other local or regional database: California Reportable Disease Information Exchange (CalREDIE)</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease, Infection: Disease-specific mortality</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease, Infection: Disease-specific mortality</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>JAMA Network Open</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>42268610</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>PMC13254740</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>https://jamanetwork.com/journals/jamanetworkopen/fullarticle/2850136</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>https://doi.org/10.1001/jamanetworkopen.2026.17684</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -5756,25 +7156,35 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>5723</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>15 countries outside of the US</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Other OUS postmarketing registry: 15 countries (Bangladesh, Bulgaria, Czech Republic,
 Estonia, Honduras, Latvia, Malaysia, New Zealand,
@@ -5782,37 +7192,47 @@
 Thailand, and Ukraine)</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>Seqirus</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>Lancet Child Adolesc Health</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>41962984</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/s2352-4642(26)00009-x</t>
         </is>
@@ -5847,62 +7267,92 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>40703</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>301 sites in 11 Northern Hemisphere countries</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
         <is>
           <t>Moderna</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>The New England Journal of Medicine</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>42090792</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42090792/</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>https://doi.org/10.1056/NEJMoa2516491</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Some Concerns: D2: Deviations from the intended interventions</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Some Concerns</t>
         </is>
       </c>
     </row>
@@ -5935,72 +7385,97 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>429595</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Kaiser Permanente (any/multiple)</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>aIIV4</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
         <is>
           <t>CSL Seqirus. All doses of Fluad adjuvanted inactivated influenza vaccine administered as part of routine clinical care for this study were donated by CSL Seqirus</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>JAMA Netw Open.</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>42081247</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>PMC13139963</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>https://jamanetwork.com/journals/jamanetworkopen/fullarticle/2848563#250984735</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>https://doi.org/10.1001/jamanetworkopen.2026.10120</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6033,72 +7508,97 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>3954</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
         <is>
           <t>The Korea University College of Medicine (Q2204881) grant funded by SK Bioscience</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>Vaccines (Basel)</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>41601017</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>PMC12846531</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12846531/</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/vaccines14010102</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -6131,57 +7631,82 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
           <t>30241</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>TriNetX EHR database</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>LAIV4</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>Human Vaccines and Immunotherapeutics</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/21645515.2026.2618341</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding; Serious: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Critical; Serious</t>
         </is>
       </c>
     </row>
@@ -6214,77 +7739,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>12477</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>post-hoc</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Other OUS postmarketing registry: DANFLU-1</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>HD-IIV4</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
         <is>
           <t>Sanofi, which provided high-dose quadrivalent influenza vaccine and a financial contribution. The trial sponsor was Copenhagen University Hospital, Herlev and Gentofte.</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>European Journal of Clinical Microbiology &amp; Infectious Diseases</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>41609947</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>PMC13222198</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/pmid/41609947/</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s10096-026-05408-5</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6317,67 +7867,92 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>7815</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>VAERS</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Safety: Guillain-Barre syndrome, Febrile seizure, Life-threatening short-term reactions, Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Safety: Guillain-Barré syndrome, Febrile seizure, Life-threatening short-term reactions, Other SAEs per study defn, Other SAEs per study defn: Death</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
         <is>
           <t>Salary by the US CDC and the US FDA.</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>41990612</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0264410X26003774?via%3Dihub</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.vaccine.2026.128569</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6406,77 +7981,102 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>08/2022 - 03/2024</t>
+          <t>9 August 2022 - 26 March 2024</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Belgium, Canada, and Spain</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>aIIV4</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Safety: Reactogenicity limiting activities of daily living (e.g., SIRVA), Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
         <is>
           <t>GSK</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>Human Vaccines &amp; Immunotherapeutics</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>41701031</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>PMC12915835</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12915835/</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/21645515.2026.2631804</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Critical: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6509,52 +8109,77 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
           <t>160435</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Other local or regional database: Pediatric Health Information System (PHIS; Children's Hospital Association, Lenexa, KS)</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
         <is>
           <t>Seattle Children's Research Institute, Center for Clinical and Translational Research, Faculty Research Support Fund Program</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>Journal of Hospital Medicine</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/jhm.70302</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6587,62 +8212,87 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>RIV4</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
         <is>
           <t>Sanofi.</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>The Lancet Infectious Diseases</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>https://www.thelancet.com/journals/laninf/article/PIIS1473-3099(26)00062-9/fulltext</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/S1473-3099(26)00062-9</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Some Concerns: D2: Deviations from the intended interventions; Some Concerns: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Some Concerns</t>
         </is>
       </c>
     </row>
@@ -6675,67 +8325,92 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>26073</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>COVID, RSV, Influenza</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>6 pediatric academic medical centers (Cincinnati, Houston, Kansas City, Nashville, Pittsburgh, and Rochester NY)</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence, Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
         <is>
           <t>This article was supported by cooperative agreements RFA-IP-16-004 and RFA-IP-21-002 from the US Centers for Disease Control and Prevention.</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>JAMA Network Open</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>40952744</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>PMC12439058</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12439058/</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>https://doi.org/10.1001/jamanetworkopen.2025.31499</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6768,52 +8443,77 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>56634</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>COVID, RSV, Influenza</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>PINC-AI Healthcare Database (PHD).</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence, Population-level disease-specific morbidity (e.g., hospitalization) and mortality</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
         <is>
           <t>Pfizer</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>Pediatric Infectious Disease Journal</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/INF.0000000000004866</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6846,60 +8546,80 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
           <t>5723</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Bangladesh, Bulgaria, Czech Republic, Estonia, Honduras, Latvia, Malaysia, New Zealand, Pakistan, the Philippines, Poland, Romania, South Africa, Thailand, Ukraine</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Other OUS postmarketing registry</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
         <is>
           <t>Seqirus UK</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>The Lancet Child and Adolescent Health</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>41962984</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/41962984/</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/S2352-4642(26)00009-X</t>
         </is>
@@ -6934,67 +8654,92 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
           <t>61814038</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Patient-level hospital discharge data for 2005-2018 in California and New York, and 2010-2018 in Georgia, from hospital associations and state health departments at the daily level.</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
         <is>
           <t>Journal of Medical Internet Research</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>41468575</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>PMC12800733</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12800733/</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>https://doi.org/10.2196/82879</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7027,62 +8772,87 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
           <t>133882</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>HD-IIV4</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Effectiveness, Safety</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
         <is>
           <t>Supported by Sanofi through a research grant to the Healthcare Research Institute of Santiago.</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>New England Journal of Medicine</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>https://www.nejm.org/doi/10.1056/NEJMoa2509834</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>https://doi.org/10.1056/NEJMoa2509834</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>High: D1: Randomization</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7110,72 +8880,97 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>04/2021 - 03/2022</t>
+          <t>13 April 2021 - 3 March 2022</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
           <t>1051</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>RCT</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>Other US postmarketing registry: V201_07 were both Phase 2, controlled, observer-blind, multicentre studies, in which adults aged ≥50 years were randomised into equal sized vaccine groups using an Interactive Response Technology, with stratification by age group (50-64 years; ≥65 years) and vaccination history (previous seasonal influenza vaccination within the past three influenza seasons [yes/no]).</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Safety: Other SAEs per study defn</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
         <is>
           <t>CSL Seqirus Inc</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>41855648</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S0264410X26002446?via%3Dihub</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.vaccine.2026.128436</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>Critical: awaiting domain decision</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7208,57 +9003,82 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>106779</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>IIV4</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
         <is>
           <t>CSL Seqirus. The journal's Rapid Service Fee was funded by CSL Seqirus.</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>Infectious Diseases and Therapy</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s40121-025-01230-2</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -7291,57 +9111,82 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>aIIV4</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Effectiveness: Infection: Disease-related hospitalization or ED visits, Infection: Lab-confirmed disease</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Effectiveness</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>Vaccine</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/science/article/pii/S2590136225001421?via%3Dihub</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jvacx.2025.100748</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding; assessment in progress</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Critical; Assessment in Progress</t>
         </is>
       </c>
     </row>
@@ -7374,74 +9219,99 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
           <t>4400</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Ecological</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Influenza</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Other local or regional database: US Naval Academy Brigade Medical Unit.
 ARIA abstracts clinical and microbiological data from MAARI patients who present for care at the BMU.
 These data are abstracted from electronic medical records and include clinical diagnoses, on-site respiratory microbiological test results, symptom type and duration, sick-in-quarters (SIQ) assignment, hospitalization, treatment, and vaccination history.</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>Influenza vaccine (unspecified)</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>Epidemiologic: Population-level disease-specific incidence and prevalence</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Epidemiologic / ecological</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
         <is>
           <t>Infectious Disease Clinical Research Program (IDCRP), DoD program executed by USU via cooperative agreement with HJF. Federal funds from Defense Health Program (HU00012120103) and Defense Health Agency AFHSD GEIS Program (grant P0064_23_HS). D. Ewing and A.K. Sundaram funded by AFHSD GEIS (ProMIS ID P0058_24_NM).</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>Influenza and Other Respiratory Viruses</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>41315053</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>PMC12981523</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12981523/</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/irv.70184</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>Critical: D1: Confounding</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16698,7 +18568,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -25845,250 +27715,290 @@
     </row>
     <row r="437">
       <c r="A437">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B437">
-        <v>5814</v>
+        <v>5810</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B438">
-        <v>5814</v>
+        <v>5810</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B439">
-        <v>5814</v>
+        <v>5810</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B440">
-        <v>5814</v>
+        <v>5810</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="B441">
-        <v>21829</v>
+        <v>5810</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Rezahosseini 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="B442">
-        <v>32935</v>
+        <v>5810</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="B443">
-        <v>32935</v>
+        <v>5810</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="B444">
-        <v>32935</v>
+        <v>5810</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="B445">
-        <v>32935</v>
+        <v>5814</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="B446">
-        <v>32935</v>
+        <v>5814</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="B447">
-        <v>32935</v>
+        <v>5814</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="B448">
-        <v>32935</v>
+        <v>5814</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449">
-        <v>268</v>
+        <v>170</v>
       </c>
       <c r="B449">
-        <v>32935</v>
+        <v>21829</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Rezahosseini 2026</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -27244,6 +29154,150 @@
         </is>
       </c>
       <c r="D513" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514">
+        <v>268</v>
+      </c>
+      <c r="B514">
+        <v>32935</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515">
+        <v>268</v>
+      </c>
+      <c r="B515">
+        <v>32935</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516">
+        <v>268</v>
+      </c>
+      <c r="B516">
+        <v>32935</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517">
+        <v>268</v>
+      </c>
+      <c r="B517">
+        <v>32935</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518">
+        <v>268</v>
+      </c>
+      <c r="B518">
+        <v>32935</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519">
+        <v>268</v>
+      </c>
+      <c r="B519">
+        <v>32935</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520">
+        <v>268</v>
+      </c>
+      <c r="B520">
+        <v>32935</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>assessment in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521">
+        <v>268</v>
+      </c>
+      <c r="B521">
+        <v>32935</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Xie 2026</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
         <is>
           <t>assessment in progress</t>
         </is>

--- a/characteristics_tables/Influenza_Study_Characteristics.xlsx
+++ b/characteristics_tables/Influenza_Study_Characteristics.xlsx
@@ -539,6 +539,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -591,12 +596,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Low; assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Low; Assessment in Progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -647,6 +652,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -745,6 +755,21 @@
           <t>Adults, Pregnant</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>84</t>
@@ -753,6 +778,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>RCT</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -878,6 +908,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -1228,6 +1263,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -1408,12 +1448,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1814,6 +1854,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -1881,12 +1926,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2045,6 +2090,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>cross-sectional</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -2159,6 +2209,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -2642,6 +2697,11 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>case series/report</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2861,7 +2921,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>March 27, 2024 and April 10, 2025</t>
+          <t>03/2024 and 04/2025</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2882,6 +2942,11 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3007,6 +3072,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -3125,6 +3195,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>retrospective cohort</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -3367,6 +3442,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>retrospective cohort</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>Influenza, COVID</t>
@@ -3434,12 +3514,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: D1: Confounding</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3490,6 +3570,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -3613,6 +3698,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>surveillance study</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>COVID, Influenza</t>
@@ -3680,12 +3770,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Critical: D1: Confounding; assessment in progress</t>
+          <t>Critical: D1: Confounding</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Critical; Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3736,6 +3826,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -3844,6 +3939,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -3952,6 +4052,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>Influenza, COVID, RSV</t>
@@ -4085,16 +4190,6 @@
           <t>Safety: Other SAEs per study defn</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Effectiveness: Infection: Lab-confirmed disease; Safety: Other SAEs per study defn</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Effectiveness, Safety</t>
-        </is>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>The study was funded by a grant from the French Ministry of Health (PHRC-N 2019). Sanofi provided the vaccines used during the study, and Sanofi laboratory (Global Clinical Immunology Platform) in Swiftwater, Pennsylvania, United States, did the testing. Sanofi had no role in the study design, data analysis, publication decision, or manuscript preparation.</t>
@@ -4108,16 +4203,6 @@
       <c r="X32" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/cid/ciag200</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Critical: awaiting domain decision</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4537,6 +4622,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>COVID, Influenza</t>
@@ -4604,12 +4694,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4778,6 +4868,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -4891,6 +4986,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -4999,6 +5099,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -5066,12 +5171,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5199,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pregnant</t>
+          <t>Adults, Pregnant</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5120,6 +5225,11 @@
       <c r="J41" t="inlineStr">
         <is>
           <t>Observational - with comparator group</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>retrospective cohort</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5220,7 +5330,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Children</t>
+          <t>Infants, Children</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5361,6 +5471,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>retrospective cohort</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>COVID, Influenza</t>
@@ -5428,12 +5543,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5602,6 +5717,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>pooled</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -5720,6 +5840,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -5787,12 +5912,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -5843,6 +5968,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>Influenza, RSV</t>
@@ -5944,7 +6074,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>24 October 2023 - 26 July 2024</t>
+          <t>10/2023 - 06/2024</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5965,6 +6095,11 @@
       <c r="J48" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -6218,6 +6353,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -6333,7 +6473,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6459,6 +6599,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -6582,6 +6727,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>retrospective cohort</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -6690,6 +6840,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>retrospective cohort</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -6775,7 +6930,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15 September 2021 - 6 June 2022</t>
+          <t>09/2021 - 06/2022</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6796,6 +6951,11 @@
       <c r="J55" t="inlineStr">
         <is>
           <t>RCT</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>primary</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6927,6 +7087,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -7028,7 +7193,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>October 1, 2024 - May 31, 2025</t>
+          <t>10/2024 - 05/2025</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7051,6 +7216,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -7118,12 +7288,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Moderate: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -7172,6 +7342,11 @@
       <c r="J58" t="inlineStr">
         <is>
           <t>RCT</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>primary</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -7285,6 +7460,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -7403,6 +7583,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -7526,6 +7711,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -7593,12 +7783,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: D1: Confounding</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7649,6 +7839,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>retrospective cohort</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -7885,6 +8080,11 @@
           <t>Non-randomized single arm</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -7981,7 +8181,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>9 August 2022 - 26 March 2024</t>
+          <t>09/2022 - 03/2024</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8002,6 +8202,11 @@
       <c r="J65" t="inlineStr">
         <is>
           <t>Non-randomized single arm</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -8230,6 +8435,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -8564,6 +8774,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -8790,6 +9005,11 @@
           <t>RCT</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>only 1 arm eligible, treated as single arm</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -8880,7 +9100,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>13 April 2021 - 3 March 2022</t>
+          <t>04/2021 - 03/2022</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8901,6 +9121,11 @@
       <c r="J73" t="inlineStr">
         <is>
           <t>RCT</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>pooled</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -9021,6 +9246,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -9073,12 +9303,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious: D1: Confounding</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -9129,6 +9359,11 @@
           <t>Observational - with comparator group</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>case-control: test‑negative design</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>Influenza</t>
@@ -9181,12 +9416,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>Critical: D1: Confounding; assessment in progress</t>
+          <t>Critical: D1: Confounding; Serious: D1: Confounding</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>Critical; Assessment in Progress</t>
+          <t>Critical; Serious</t>
         </is>
       </c>
     </row>
@@ -12780,7 +13015,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -13527,401 +13762,417 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="B47">
-        <v>5196</v>
+        <v>500</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bonduelle 2025</t>
+          <t>Sayers 2026</t>
         </is>
       </c>
       <c r="D47">
-        <v>59</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="B48">
-        <v>522</v>
+        <v>5196</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Faksova 2026</t>
+          <t>Bonduelle 2025</t>
         </is>
       </c>
       <c r="D48">
-        <v>2329372</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="B49">
-        <v>5246</v>
+        <v>522</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palma-Garcia 2025</t>
+          <t>Faksova 2026</t>
         </is>
       </c>
       <c r="D49">
-        <v>287661</v>
+        <v>2329372</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B50">
-        <v>5422</v>
+        <v>5246</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chime 2025</t>
+          <t>Palma-Garcia 2025</t>
         </is>
       </c>
       <c r="D50">
-        <v>1539</v>
+        <v>287661</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B51">
-        <v>5445</v>
+        <v>5422</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Branche 2025</t>
+          <t>Chime 2025</t>
         </is>
       </c>
       <c r="D51">
-        <v>436</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B52">
-        <v>5751</v>
+        <v>5445</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Branche 2025</t>
         </is>
       </c>
       <c r="D52">
-        <v>1106628</v>
+        <v>436</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B53">
-        <v>5803</v>
+        <v>5751</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poder 2026</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D53">
-        <v>5723</v>
+        <v>1106628</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B54">
-        <v>5810</v>
+        <v>5803</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Poder 2026</t>
         </is>
       </c>
       <c r="D54">
-        <v>40703</v>
+        <v>5723</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B55">
-        <v>5814</v>
+        <v>5810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D55">
-        <v>429595</v>
+        <v>40703</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="B56">
-        <v>589</v>
+        <v>5814</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Choi 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D56">
-        <v>3954</v>
+        <v>429595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B57">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kitano 2026</t>
+          <t>Choi 2026</t>
         </is>
       </c>
       <c r="D57">
-        <v>30241</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B58">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bernholm 2026</t>
+          <t>Kitano 2026</t>
         </is>
       </c>
       <c r="D58">
-        <v>12477</v>
+        <v>30241</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="B59">
-        <v>61</v>
+        <v>602</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Anyalechi 2026</t>
+          <t>Bernholm 2026</t>
         </is>
       </c>
       <c r="D59">
-        <v>7815</v>
+        <v>12477</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B60">
-        <v>632</v>
+        <v>61</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Anyalechi 2026</t>
         </is>
       </c>
       <c r="D60">
-        <v>324</v>
+        <v>7815</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B61">
-        <v>647</v>
+        <v>632</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Money 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D61">
-        <v>160435</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B62">
-        <v>692</v>
+        <v>647</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sullivan 2026</t>
+          <t>Money 2026</t>
         </is>
       </c>
       <c r="D62">
-        <v>359</v>
+        <v>160435</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Sullivan 2026</t>
         </is>
       </c>
       <c r="D63">
-        <v>26073</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B64">
-        <v>71</v>
+        <v>703</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D64">
-        <v>56634</v>
+        <v>26073</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65">
         <v>71</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poder 2026</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D65">
-        <v>5723</v>
+        <v>56634</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="B66">
-        <v>794</v>
+        <v>71</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Huang 2025</t>
+          <t>Poder 2026</t>
         </is>
       </c>
       <c r="D66">
-        <v>61814038</v>
+        <v>5723</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67">
-        <v>826</v>
+        <v>794</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pardo-Seco 2025</t>
+          <t>Huang 2025</t>
         </is>
       </c>
       <c r="D67">
-        <v>133882</v>
+        <v>61814038</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="B68">
-        <v>87</v>
+        <v>826</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>deLooze 2026</t>
+          <t>Pardo-Seco 2025</t>
         </is>
       </c>
       <c r="D68">
-        <v>1051</v>
+        <v>133882</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B69">
-        <v>897</v>
+        <v>87</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Stein 2025</t>
+          <t>deLooze 2026</t>
         </is>
       </c>
       <c r="D69">
-        <v>106779</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B70">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Domnich 2025</t>
+          <t>Stein 2025</t>
         </is>
       </c>
       <c r="D70">
-        <v>1339</v>
+        <v>106779</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
+        <v>84</v>
+      </c>
+      <c r="B71">
+        <v>927</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Domnich 2025</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
         <v>85</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>945</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Pollett 2025</t>
         </is>
       </c>
-      <c r="D71">
+      <c r="D72">
         <v>4400</v>
       </c>
     </row>
@@ -13932,7 +14183,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -15645,74 +15896,74 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B96">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Leonard 2026</t>
+          <t>Zhang 2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>268</v>
+        <v>34</v>
       </c>
       <c r="B97">
-        <v>32935</v>
+        <v>329</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Leonard 2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>268</v>
+        <v>34</v>
       </c>
       <c r="B98">
-        <v>32935</v>
+        <v>329</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Leonard 2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="B99">
-        <v>33</v>
+        <v>32935</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Xu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -15723,32 +15974,32 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>38</v>
+        <v>268</v>
       </c>
       <c r="B100">
-        <v>366</v>
+        <v>32935</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Caswell 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="B101">
-        <v>3947</v>
+        <v>33</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xu 2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -15759,19 +16010,19 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="B102">
-        <v>3947</v>
+        <v>366</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Caswell 2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -15789,7 +16040,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
@@ -15807,79 +16058,79 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B105">
-        <v>4110</v>
+        <v>3947</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="B106">
-        <v>423</v>
+        <v>3947</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="B107">
-        <v>433</v>
+        <v>4110</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hayek 2026</t>
+          <t>Comstock 2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B108">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hayek 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
@@ -15897,92 +16148,92 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="B110">
-        <v>4748</v>
+        <v>433</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Hayek 2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="B111">
-        <v>4748</v>
+        <v>433</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Hayek 2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="B112">
-        <v>500</v>
+        <v>4748</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sayers 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="B113">
-        <v>500</v>
+        <v>4748</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sayers 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>IC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="B114">
-        <v>5196</v>
+        <v>500</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bonduelle 2025</t>
+          <t>Sayers 2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15993,122 +16244,122 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B115">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Faksova 2026</t>
+          <t>Sayers 2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="B116">
-        <v>522</v>
+        <v>5196</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Faksova 2026</t>
+          <t>Bonduelle 2025</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="B117">
-        <v>5246</v>
+        <v>522</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Palma-Garcia 2025</t>
+          <t>Faksova 2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="B118">
-        <v>5246</v>
+        <v>522</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Palma-Garcia 2025</t>
+          <t>Faksova 2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B119">
-        <v>5422</v>
+        <v>5246</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chime 2025</t>
+          <t>Palma-Garcia 2025</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B120">
-        <v>5445</v>
+        <v>5246</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Branche 2025</t>
+          <t>Palma-Garcia 2025</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B121">
-        <v>5445</v>
+        <v>5422</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Branche 2025</t>
+          <t>Chime 2025</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16119,14 +16370,14 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B122">
-        <v>5751</v>
+        <v>5445</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Branche 2025</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16137,14 +16388,14 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B123">
-        <v>5751</v>
+        <v>5445</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Branche 2025</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16167,7 +16418,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
@@ -16185,20 +16436,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B126">
-        <v>5803</v>
+        <v>5751</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Poder 2026</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16209,14 +16460,14 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B127">
-        <v>5803</v>
+        <v>5751</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Poder 2026</t>
+          <t>Zhu 2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16227,50 +16478,50 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B128">
-        <v>5810</v>
+        <v>5803</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Poder 2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B129">
-        <v>5814</v>
+        <v>5803</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hsiao 2026</t>
+          <t>Poder 2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="B130">
-        <v>589</v>
+        <v>5810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Choi 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -16281,163 +16532,163 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="B131">
-        <v>590</v>
+        <v>5814</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kitano 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B132">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kitano 2026</t>
+          <t>Choi 2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B133">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bernholm 2026</t>
+          <t>Kitano 2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="B134">
-        <v>61</v>
+        <v>590</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Anyalechi 2026</t>
+          <t>Kitano 2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="B135">
-        <v>61</v>
+        <v>602</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Anyalechi 2026</t>
+          <t>Bernholm 2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B136">
-        <v>632</v>
+        <v>61</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Anyalechi 2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B137">
-        <v>632</v>
+        <v>61</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Anyalechi 2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B138">
-        <v>647</v>
+        <v>632</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Money 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B139">
-        <v>647</v>
+        <v>632</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Money 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -16455,74 +16706,74 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B141">
-        <v>692</v>
+        <v>647</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sullivan 2026</t>
+          <t>Money 2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B142">
-        <v>703</v>
+        <v>647</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Money 2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B143">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Sullivan 2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B144">
-        <v>71</v>
+        <v>703</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -16533,32 +16784,32 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="B145">
-        <v>71</v>
+        <v>703</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B146">
         <v>71</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Poder 2026</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -16569,55 +16820,55 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B147">
         <v>71</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Poder 2026</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>IC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="B148">
-        <v>794</v>
+        <v>71</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Huang 2025</t>
+          <t>Poder 2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="B149">
-        <v>794</v>
+        <v>71</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Huang 2025</t>
+          <t>Poder 2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16886,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
@@ -16653,74 +16904,74 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B152">
-        <v>826</v>
+        <v>794</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pardo-Seco 2025</t>
+          <t>Huang 2025</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="B153">
-        <v>87</v>
+        <v>794</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>deLooze 2026</t>
+          <t>Huang 2025</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="B154">
-        <v>87</v>
+        <v>826</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>deLooze 2026</t>
+          <t>Pardo-Seco 2025</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B155">
-        <v>897</v>
+        <v>87</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Stein 2025</t>
+          <t>deLooze 2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -16731,14 +16982,14 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B156">
-        <v>897</v>
+        <v>87</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Stein 2025</t>
+          <t>deLooze 2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -16761,7 +17012,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
@@ -16779,7 +17030,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -16797,43 +17048,43 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B160">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Domnich 2025</t>
+          <t>Stein 2025</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B161">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Domnich 2025</t>
+          <t>Stein 2025</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -16851,23 +17102,59 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>OA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163">
+        <v>84</v>
+      </c>
+      <c r="B163">
+        <v>927</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Domnich 2025</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>84</v>
+      </c>
+      <c r="B164">
+        <v>927</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Domnich 2025</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
         <v>85</v>
       </c>
-      <c r="B163">
+      <c r="B165">
         <v>945</v>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>Pollett 2025</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -18568,7 +18855,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E521"/>
+  <dimension ref="A1:E412"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -20584,7 +20871,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20894,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20620,7 +20917,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20940,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20656,7 +20963,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20986,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20692,7 +21009,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20710,7 +21032,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20728,7 +21055,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20746,7 +21078,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20764,7 +21101,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20782,7 +21124,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20800,7 +21147,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20818,7 +21170,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20836,7 +21193,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20854,7 +21216,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20872,7 +21239,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20890,7 +21262,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20908,7 +21285,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20926,7 +21308,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20944,7 +21331,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20962,7 +21354,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20980,7 +21377,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -20998,7 +21400,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -21660,7 +22067,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -21678,7 +22090,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -21696,7 +22113,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -21714,7 +22136,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -21778,7 +22205,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -21796,7 +22228,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -21927,7 +22364,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21945,7 +22382,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21963,7 +22400,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21981,7 +22418,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22574,7 +23011,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22592,7 +23029,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22610,7 +23047,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22628,7 +23065,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22646,7 +23083,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22664,7 +23101,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22682,7 +23119,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22700,7 +23137,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22718,7 +23155,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22736,7 +23173,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22754,7 +23191,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22772,7 +23209,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22790,7 +23227,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -23026,230 +23463,290 @@
     </row>
     <row r="209">
       <c r="A209">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B209">
-        <v>1240</v>
+        <v>1322</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Lopez 2025</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B210">
-        <v>1240</v>
+        <v>1322</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Lopez 2025</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B211">
-        <v>1240</v>
+        <v>1322</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Lopez 2025</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B212">
-        <v>1240</v>
+        <v>1322</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Lopez 2025</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B213">
-        <v>1240</v>
+        <v>1322</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Lopez 2025</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B214">
-        <v>1240</v>
+        <v>1322</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Lopez 2025</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B215">
-        <v>1240</v>
+        <v>1418</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Reinhart 2025</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B216">
-        <v>1240</v>
+        <v>1418</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Reinhart 2025</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B217">
-        <v>1240</v>
+        <v>1420</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Fazal 2025</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B218">
-        <v>1240</v>
+        <v>1420</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Fazal 2025</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B219">
-        <v>1240</v>
+        <v>1420</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Fazal 2025</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B220">
-        <v>1240</v>
+        <v>1420</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Gaglani 2025</t>
+          <t>Fazal 2025</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B221">
-        <v>1322</v>
+        <v>1420</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Lopez 2025</t>
+          <t>Fazal 2025</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -23265,14 +23762,14 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B222">
-        <v>1322</v>
+        <v>1420</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Lopez 2025</t>
+          <t>Fazal 2025</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -23288,14 +23785,14 @@
     </row>
     <row r="223">
       <c r="A223">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B223">
-        <v>1322</v>
+        <v>1429</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Lopez 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -23311,14 +23808,14 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B224">
-        <v>1322</v>
+        <v>1429</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Lopez 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -23334,19 +23831,19 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B225">
-        <v>1322</v>
+        <v>1429</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Lopez 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -23357,19 +23854,19 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B226">
-        <v>1322</v>
+        <v>1429</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Lopez 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -23380,14 +23877,14 @@
     </row>
     <row r="227">
       <c r="A227">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B227">
-        <v>1418</v>
+        <v>1429</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Reinhart 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -23403,14 +23900,14 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B228">
-        <v>1418</v>
+        <v>1429</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Reinhart 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -23426,14 +23923,14 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B229">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Fazal 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -23449,14 +23946,14 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B230">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Fazal 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -23472,14 +23969,14 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B231">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Fazal 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -23495,14 +23992,14 @@
     </row>
     <row r="232">
       <c r="A232">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B232">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Fazal 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -23518,14 +24015,14 @@
     </row>
     <row r="233">
       <c r="A233">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B233">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Fazal 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -23541,14 +24038,14 @@
     </row>
     <row r="234">
       <c r="A234">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B234">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Fazal 2025</t>
+          <t>Lloyd 2025</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -23587,14 +24084,14 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B236">
-        <v>1429</v>
+        <v>1441</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>O'Halloran 2025</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -23610,14 +24107,14 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B237">
-        <v>1429</v>
+        <v>1441</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>O'Halloran 2025</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -23633,14 +24130,14 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B238">
-        <v>1429</v>
+        <v>1441</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>O'Halloran 2025</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -23656,14 +24153,14 @@
     </row>
     <row r="239">
       <c r="A239">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B239">
-        <v>1429</v>
+        <v>1441</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>O'Halloran 2025</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -23679,83 +24176,83 @@
     </row>
     <row r="240">
       <c r="A240">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B240">
-        <v>1429</v>
+        <v>1572</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Choi 2025</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B241">
-        <v>1429</v>
+        <v>1572</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Choi 2025</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B242">
-        <v>1429</v>
+        <v>1572</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Choi 2025</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B243">
-        <v>1429</v>
+        <v>1647</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Zerbo 2025</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -23771,14 +24268,14 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B244">
-        <v>1429</v>
+        <v>1647</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Zerbo 2025</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -23794,14 +24291,14 @@
     </row>
     <row r="245">
       <c r="A245">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B245">
-        <v>1429</v>
+        <v>1647</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Zerbo 2025</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -23817,14 +24314,14 @@
     </row>
     <row r="246">
       <c r="A246">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B246">
-        <v>1429</v>
+        <v>1647</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Zerbo 2025</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -23840,14 +24337,14 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B247">
-        <v>1429</v>
+        <v>1647</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Lloyd 2025</t>
+          <t>Zerbo 2025</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -23863,14 +24360,14 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B248">
-        <v>1441</v>
+        <v>1664</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>O'Halloran 2025</t>
+          <t>Schnake-Mahl 2025</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -23886,14 +24383,14 @@
     </row>
     <row r="249">
       <c r="A249">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B249">
-        <v>1441</v>
+        <v>1664</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>O'Halloran 2025</t>
+          <t>Schnake-Mahl 2025</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -23909,14 +24406,14 @@
     </row>
     <row r="250">
       <c r="A250">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B250">
-        <v>1441</v>
+        <v>1664</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>O'Halloran 2025</t>
+          <t>Schnake-Mahl 2025</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -23932,14 +24429,14 @@
     </row>
     <row r="251">
       <c r="A251">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B251">
-        <v>1441</v>
+        <v>1664</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>O'Halloran 2025</t>
+          <t>Schnake-Mahl 2025</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -23955,83 +24452,83 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B252">
-        <v>1572</v>
+        <v>1905</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Choi 2025</t>
+          <t>Munjal 2025</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B253">
-        <v>1572</v>
+        <v>1920</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Choi 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B254">
-        <v>1572</v>
+        <v>1920</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Choi 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B255">
-        <v>1647</v>
+        <v>1920</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Zerbo 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -24047,14 +24544,14 @@
     </row>
     <row r="256">
       <c r="A256">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B256">
-        <v>1647</v>
+        <v>1920</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Zerbo 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -24070,14 +24567,14 @@
     </row>
     <row r="257">
       <c r="A257">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B257">
-        <v>1647</v>
+        <v>1920</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Zerbo 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -24093,14 +24590,14 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B258">
-        <v>1647</v>
+        <v>1920</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Zerbo 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -24116,14 +24613,14 @@
     </row>
     <row r="259">
       <c r="A259">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B259">
-        <v>1647</v>
+        <v>1920</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Zerbo 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -24139,14 +24636,14 @@
     </row>
     <row r="260">
       <c r="A260">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B260">
-        <v>1664</v>
+        <v>1920</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Schnake-Mahl 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -24162,14 +24659,14 @@
     </row>
     <row r="261">
       <c r="A261">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B261">
-        <v>1664</v>
+        <v>1920</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Schnake-Mahl 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -24185,14 +24682,14 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B262">
-        <v>1664</v>
+        <v>1920</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Schnake-Mahl 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -24208,14 +24705,14 @@
     </row>
     <row r="263">
       <c r="A263">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B263">
-        <v>1664</v>
+        <v>1920</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Schnake-Mahl 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -24231,19 +24728,24 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B264">
-        <v>1905</v>
+        <v>1920</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Munjal 2025</t>
+          <t>Fu 2025</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -24410,14 +24912,14 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B272">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -24433,14 +24935,14 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B273">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -24456,14 +24958,14 @@
     </row>
     <row r="274">
       <c r="A274">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B274">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -24479,14 +24981,14 @@
     </row>
     <row r="275">
       <c r="A275">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B275">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -24502,14 +25004,14 @@
     </row>
     <row r="276">
       <c r="A276">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B276">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -24525,14 +25027,14 @@
     </row>
     <row r="277">
       <c r="A277">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B277">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -24548,14 +25050,14 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B278">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -24571,14 +25073,14 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B279">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -24594,14 +25096,14 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B280">
-        <v>1920</v>
+        <v>1960</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>SalamancadelaCueva 2025</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -24617,14 +25119,14 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B281">
-        <v>1920</v>
+        <v>1969</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Jain 2025</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -24640,14 +25142,14 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B282">
-        <v>1920</v>
+        <v>1969</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Jain 2025</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -24663,14 +25165,14 @@
     </row>
     <row r="283">
       <c r="A283">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B283">
-        <v>1920</v>
+        <v>1969</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Fu 2025</t>
+          <t>Jain 2025</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -24686,14 +25188,14 @@
     </row>
     <row r="284">
       <c r="A284">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B284">
-        <v>1924</v>
+        <v>1970</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -24709,14 +25211,14 @@
     </row>
     <row r="285">
       <c r="A285">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B285">
-        <v>1924</v>
+        <v>1970</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -24732,14 +25234,14 @@
     </row>
     <row r="286">
       <c r="A286">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B286">
-        <v>1924</v>
+        <v>1970</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -24755,14 +25257,14 @@
     </row>
     <row r="287">
       <c r="A287">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B287">
-        <v>1924</v>
+        <v>2150</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -24778,14 +25280,14 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B288">
-        <v>1924</v>
+        <v>2150</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -24801,14 +25303,14 @@
     </row>
     <row r="289">
       <c r="A289">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B289">
-        <v>1924</v>
+        <v>2150</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -24824,50 +25326,60 @@
     </row>
     <row r="290">
       <c r="A290">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B290">
-        <v>1924</v>
+        <v>2150</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B291">
-        <v>1924</v>
+        <v>2150</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B292">
-        <v>1960</v>
+        <v>2150</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>SalamancadelaCueva 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -24883,14 +25395,14 @@
     </row>
     <row r="293">
       <c r="A293">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B293">
-        <v>1969</v>
+        <v>2150</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jain 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -24906,14 +25418,14 @@
     </row>
     <row r="294">
       <c r="A294">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B294">
-        <v>1969</v>
+        <v>2150</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jain 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -24929,14 +25441,14 @@
     </row>
     <row r="295">
       <c r="A295">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B295">
-        <v>1969</v>
+        <v>2150</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Jain 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -24952,14 +25464,14 @@
     </row>
     <row r="296">
       <c r="A296">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B296">
-        <v>1970</v>
+        <v>2150</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -24975,14 +25487,14 @@
     </row>
     <row r="297">
       <c r="A297">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B297">
-        <v>1970</v>
+        <v>2150</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -24998,14 +25510,14 @@
     </row>
     <row r="298">
       <c r="A298">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B298">
-        <v>1970</v>
+        <v>2150</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -25021,14 +25533,14 @@
     </row>
     <row r="299">
       <c r="A299">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B299">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -25044,14 +25556,14 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B300">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -25067,14 +25579,14 @@
     </row>
     <row r="301">
       <c r="A301">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B301">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -25090,14 +25602,14 @@
     </row>
     <row r="302">
       <c r="A302">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B302">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -25113,14 +25625,14 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B303">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -25136,14 +25648,14 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B304">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -25159,14 +25671,14 @@
     </row>
     <row r="305">
       <c r="A305">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B305">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -25182,14 +25694,14 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B306">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -25205,14 +25717,14 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B307">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -25228,14 +25740,14 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B308">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -25251,14 +25763,14 @@
     </row>
     <row r="309">
       <c r="A309">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B309">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -25274,14 +25786,14 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B310">
-        <v>2150</v>
+        <v>2420</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Brown 2026</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -25320,3986 +25832,1964 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B312">
-        <v>2420</v>
+        <v>2680</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Folegatti 2026</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B313">
-        <v>2420</v>
+        <v>2680</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Folegatti 2026</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B314">
-        <v>2420</v>
+        <v>4110</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Comstock 2026</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B315">
-        <v>2420</v>
+        <v>4110</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Comstock 2026</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B316">
-        <v>2420</v>
+        <v>4110</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Comstock 2026</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B317">
-        <v>2420</v>
+        <v>4110</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Comstock 2026</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B318">
-        <v>2420</v>
+        <v>4748</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B319">
-        <v>2420</v>
+        <v>4748</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B320">
-        <v>2420</v>
+        <v>4748</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B321">
-        <v>2420</v>
+        <v>4748</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B322">
-        <v>2420</v>
+        <v>4748</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B323">
-        <v>2420</v>
+        <v>4748</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Brown 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B324">
-        <v>2680</v>
+        <v>4748</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Folegatti 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B325">
-        <v>2680</v>
+        <v>4748</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Folegatti 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B326">
-        <v>3183</v>
+        <v>4748</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Yingyounyong 2025</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B327">
-        <v>3183</v>
+        <v>5196</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Bonduelle 2025</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B328">
-        <v>3183</v>
+        <v>5422</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Chime 2025</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B329">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B330">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B331">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B332">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B333">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B334">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B335">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B336">
-        <v>3183</v>
+        <v>5810</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B337">
-        <v>3183</v>
+        <v>5814</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B338">
-        <v>3183</v>
+        <v>5814</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B339">
-        <v>3183</v>
+        <v>5814</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B340">
-        <v>3183</v>
+        <v>5814</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Hsiao 2026</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B341">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B342">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B343">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B344">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B345">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B346">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B347">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B348">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B349">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B350">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B351">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B352">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B353">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B354">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B355">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B356">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B357">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B358">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B359">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B360">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B361">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B362">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B363">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B364">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B365">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B366">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B367">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B368">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B369">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B370">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B371">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B372">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B373">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B374">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B375">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="B376">
-        <v>3183</v>
+        <v>32935</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Maloney 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B377">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B378">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B379">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B380">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B381">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B382">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B383">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B384">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B385">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B386">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B387">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B388">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B389">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B390">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B391">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B392">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B393">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B394">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B395">
-        <v>3947</v>
+        <v>32935</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="B396">
-        <v>4110</v>
+        <v>32935</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="B397">
-        <v>4110</v>
+        <v>32935</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="B398">
-        <v>4110</v>
+        <v>32935</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="B399">
-        <v>4110</v>
+        <v>32935</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B400">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B401">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B402">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B403">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B404">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B405">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B406">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B407">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="B408">
-        <v>4748</v>
+        <v>32935</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Yingyounyong 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>135</v>
+        <v>268</v>
       </c>
       <c r="B409">
-        <v>5196</v>
+        <v>32935</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Bonduelle 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>137</v>
+        <v>268</v>
       </c>
       <c r="B410">
-        <v>5422</v>
+        <v>32935</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Chime 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="B411">
-        <v>5751</v>
+        <v>32935</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="B412">
-        <v>5751</v>
+        <v>32935</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Zhu 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413">
-        <v>139</v>
-      </c>
-      <c r="B413">
-        <v>5751</v>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414">
-        <v>139</v>
-      </c>
-      <c r="B414">
-        <v>5751</v>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415">
-        <v>139</v>
-      </c>
-      <c r="B415">
-        <v>5751</v>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416">
-        <v>139</v>
-      </c>
-      <c r="B416">
-        <v>5751</v>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417">
-        <v>139</v>
-      </c>
-      <c r="B417">
-        <v>5751</v>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418">
-        <v>139</v>
-      </c>
-      <c r="B418">
-        <v>5751</v>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419">
-        <v>139</v>
-      </c>
-      <c r="B419">
-        <v>5751</v>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420">
-        <v>139</v>
-      </c>
-      <c r="B420">
-        <v>5751</v>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421">
-        <v>139</v>
-      </c>
-      <c r="B421">
-        <v>5751</v>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422">
-        <v>139</v>
-      </c>
-      <c r="B422">
-        <v>5751</v>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423">
-        <v>139</v>
-      </c>
-      <c r="B423">
-        <v>5751</v>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424">
-        <v>139</v>
-      </c>
-      <c r="B424">
-        <v>5751</v>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425">
-        <v>139</v>
-      </c>
-      <c r="B425">
-        <v>5751</v>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426">
-        <v>139</v>
-      </c>
-      <c r="B426">
-        <v>5751</v>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427">
-        <v>139</v>
-      </c>
-      <c r="B427">
-        <v>5751</v>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428">
-        <v>139</v>
-      </c>
-      <c r="B428">
-        <v>5751</v>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429">
-        <v>139</v>
-      </c>
-      <c r="B429">
-        <v>5751</v>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430">
-        <v>139</v>
-      </c>
-      <c r="B430">
-        <v>5751</v>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431">
-        <v>139</v>
-      </c>
-      <c r="B431">
-        <v>5751</v>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432">
-        <v>139</v>
-      </c>
-      <c r="B432">
-        <v>5751</v>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433">
-        <v>139</v>
-      </c>
-      <c r="B433">
-        <v>5751</v>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434">
-        <v>139</v>
-      </c>
-      <c r="B434">
-        <v>5751</v>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435">
-        <v>139</v>
-      </c>
-      <c r="B435">
-        <v>5751</v>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436">
-        <v>139</v>
-      </c>
-      <c r="B436">
-        <v>5751</v>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>Zhu 2026</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437">
-        <v>141</v>
-      </c>
-      <c r="B437">
-        <v>5810</v>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438">
-        <v>141</v>
-      </c>
-      <c r="B438">
-        <v>5810</v>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439">
-        <v>141</v>
-      </c>
-      <c r="B439">
-        <v>5810</v>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440">
-        <v>141</v>
-      </c>
-      <c r="B440">
-        <v>5810</v>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441">
-        <v>141</v>
-      </c>
-      <c r="B441">
-        <v>5810</v>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442">
-        <v>141</v>
-      </c>
-      <c r="B442">
-        <v>5810</v>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443">
-        <v>141</v>
-      </c>
-      <c r="B443">
-        <v>5810</v>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444">
-        <v>141</v>
-      </c>
-      <c r="B444">
-        <v>5810</v>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>Leroux-Roels 2026</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445">
-        <v>142</v>
-      </c>
-      <c r="B445">
-        <v>5814</v>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>Hsiao 2026</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446">
-        <v>142</v>
-      </c>
-      <c r="B446">
-        <v>5814</v>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>Hsiao 2026</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447">
-        <v>142</v>
-      </c>
-      <c r="B447">
-        <v>5814</v>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>Hsiao 2026</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448">
-        <v>142</v>
-      </c>
-      <c r="B448">
-        <v>5814</v>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>Hsiao 2026</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449">
-        <v>170</v>
-      </c>
-      <c r="B449">
-        <v>21829</v>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>Rezahosseini 2026</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450">
-        <v>268</v>
-      </c>
-      <c r="B450">
-        <v>32935</v>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451">
-        <v>268</v>
-      </c>
-      <c r="B451">
-        <v>32935</v>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452">
-        <v>268</v>
-      </c>
-      <c r="B452">
-        <v>32935</v>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453">
-        <v>268</v>
-      </c>
-      <c r="B453">
-        <v>32935</v>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454">
-        <v>268</v>
-      </c>
-      <c r="B454">
-        <v>32935</v>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455">
-        <v>268</v>
-      </c>
-      <c r="B455">
-        <v>32935</v>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456">
-        <v>268</v>
-      </c>
-      <c r="B456">
-        <v>32935</v>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457">
-        <v>268</v>
-      </c>
-      <c r="B457">
-        <v>32935</v>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458">
-        <v>268</v>
-      </c>
-      <c r="B458">
-        <v>32935</v>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459">
-        <v>268</v>
-      </c>
-      <c r="B459">
-        <v>32935</v>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460">
-        <v>268</v>
-      </c>
-      <c r="B460">
-        <v>32935</v>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461">
-        <v>268</v>
-      </c>
-      <c r="B461">
-        <v>32935</v>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462">
-        <v>268</v>
-      </c>
-      <c r="B462">
-        <v>32935</v>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463">
-        <v>268</v>
-      </c>
-      <c r="B463">
-        <v>32935</v>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464">
-        <v>268</v>
-      </c>
-      <c r="B464">
-        <v>32935</v>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465">
-        <v>268</v>
-      </c>
-      <c r="B465">
-        <v>32935</v>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466">
-        <v>268</v>
-      </c>
-      <c r="B466">
-        <v>32935</v>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467">
-        <v>268</v>
-      </c>
-      <c r="B467">
-        <v>32935</v>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468">
-        <v>268</v>
-      </c>
-      <c r="B468">
-        <v>32935</v>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469">
-        <v>268</v>
-      </c>
-      <c r="B469">
-        <v>32935</v>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470">
-        <v>268</v>
-      </c>
-      <c r="B470">
-        <v>32935</v>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471">
-        <v>268</v>
-      </c>
-      <c r="B471">
-        <v>32935</v>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472">
-        <v>268</v>
-      </c>
-      <c r="B472">
-        <v>32935</v>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473">
-        <v>268</v>
-      </c>
-      <c r="B473">
-        <v>32935</v>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474">
-        <v>268</v>
-      </c>
-      <c r="B474">
-        <v>32935</v>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475">
-        <v>268</v>
-      </c>
-      <c r="B475">
-        <v>32935</v>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476">
-        <v>268</v>
-      </c>
-      <c r="B476">
-        <v>32935</v>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477">
-        <v>268</v>
-      </c>
-      <c r="B477">
-        <v>32935</v>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478">
-        <v>268</v>
-      </c>
-      <c r="B478">
-        <v>32935</v>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479">
-        <v>268</v>
-      </c>
-      <c r="B479">
-        <v>32935</v>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480">
-        <v>268</v>
-      </c>
-      <c r="B480">
-        <v>32935</v>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481">
-        <v>268</v>
-      </c>
-      <c r="B481">
-        <v>32935</v>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482">
-        <v>268</v>
-      </c>
-      <c r="B482">
-        <v>32935</v>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483">
-        <v>268</v>
-      </c>
-      <c r="B483">
-        <v>32935</v>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484">
-        <v>268</v>
-      </c>
-      <c r="B484">
-        <v>32935</v>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485">
-        <v>268</v>
-      </c>
-      <c r="B485">
-        <v>32935</v>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486">
-        <v>268</v>
-      </c>
-      <c r="B486">
-        <v>32935</v>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487">
-        <v>268</v>
-      </c>
-      <c r="B487">
-        <v>32935</v>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488">
-        <v>268</v>
-      </c>
-      <c r="B488">
-        <v>32935</v>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489">
-        <v>268</v>
-      </c>
-      <c r="B489">
-        <v>32935</v>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490">
-        <v>268</v>
-      </c>
-      <c r="B490">
-        <v>32935</v>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491">
-        <v>268</v>
-      </c>
-      <c r="B491">
-        <v>32935</v>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492">
-        <v>268</v>
-      </c>
-      <c r="B492">
-        <v>32935</v>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493">
-        <v>268</v>
-      </c>
-      <c r="B493">
-        <v>32935</v>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494">
-        <v>268</v>
-      </c>
-      <c r="B494">
-        <v>32935</v>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495">
-        <v>268</v>
-      </c>
-      <c r="B495">
-        <v>32935</v>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496">
-        <v>268</v>
-      </c>
-      <c r="B496">
-        <v>32935</v>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497">
-        <v>268</v>
-      </c>
-      <c r="B497">
-        <v>32935</v>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498">
-        <v>268</v>
-      </c>
-      <c r="B498">
-        <v>32935</v>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499">
-        <v>268</v>
-      </c>
-      <c r="B499">
-        <v>32935</v>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500">
-        <v>268</v>
-      </c>
-      <c r="B500">
-        <v>32935</v>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501">
-        <v>268</v>
-      </c>
-      <c r="B501">
-        <v>32935</v>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502">
-        <v>268</v>
-      </c>
-      <c r="B502">
-        <v>32935</v>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503">
-        <v>268</v>
-      </c>
-      <c r="B503">
-        <v>32935</v>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504">
-        <v>268</v>
-      </c>
-      <c r="B504">
-        <v>32935</v>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505">
-        <v>268</v>
-      </c>
-      <c r="B505">
-        <v>32935</v>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506">
-        <v>268</v>
-      </c>
-      <c r="B506">
-        <v>32935</v>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507">
-        <v>268</v>
-      </c>
-      <c r="B507">
-        <v>32935</v>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508">
-        <v>268</v>
-      </c>
-      <c r="B508">
-        <v>32935</v>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509">
-        <v>268</v>
-      </c>
-      <c r="B509">
-        <v>32935</v>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510">
-        <v>268</v>
-      </c>
-      <c r="B510">
-        <v>32935</v>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511">
-        <v>268</v>
-      </c>
-      <c r="B511">
-        <v>32935</v>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512">
-        <v>268</v>
-      </c>
-      <c r="B512">
-        <v>32935</v>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513">
-        <v>268</v>
-      </c>
-      <c r="B513">
-        <v>32935</v>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514">
-        <v>268</v>
-      </c>
-      <c r="B514">
-        <v>32935</v>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515">
-        <v>268</v>
-      </c>
-      <c r="B515">
-        <v>32935</v>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516">
-        <v>268</v>
-      </c>
-      <c r="B516">
-        <v>32935</v>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517">
-        <v>268</v>
-      </c>
-      <c r="B517">
-        <v>32935</v>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518">
-        <v>268</v>
-      </c>
-      <c r="B518">
-        <v>32935</v>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519">
-        <v>268</v>
-      </c>
-      <c r="B519">
-        <v>32935</v>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520">
-        <v>268</v>
-      </c>
-      <c r="B520">
-        <v>32935</v>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521">
-        <v>268</v>
-      </c>
-      <c r="B521">
-        <v>32935</v>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>

--- a/characteristics_tables/Influenza_Study_Characteristics.xlsx
+++ b/characteristics_tables/Influenza_Study_Characteristics.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>only 1 arm eligible, treated as single arm</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Non-randomized single arm</t>
+          <t>Observational - with comparator group</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>case series/report</t>
+          <t>SCCS (self-controlled case series)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>only 1 arm eligible, treated as single arm</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">

--- a/characteristics_tables/Influenza_Study_Characteristics.xlsx
+++ b/characteristics_tables/Influenza_Study_Characteristics.xlsx
@@ -1818,7 +1818,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13">
         <v>1259</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14">
         <v>1322</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B15">
         <v>1344</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B17">
         <v>1418</v>
@@ -2425,7 +2425,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B18">
         <v>1420</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19">
         <v>1429</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B20">
         <v>1441</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B21">
         <v>1506</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B22">
         <v>1572</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B23">
         <v>1647</v>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B24">
         <v>1664</v>
@@ -3290,7 +3290,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B25">
         <v>1905</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26">
         <v>1920</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B27">
         <v>1924</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28">
         <v>1960</v>
@@ -3788,7 +3788,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29">
         <v>1969</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30">
         <v>1970</v>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33">
         <v>2150</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B34">
         <v>21829</v>
@@ -4511,7 +4511,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B35">
         <v>2420</v>
@@ -4629,7 +4629,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B36">
         <v>2680</v>
@@ -4860,7 +4860,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B38">
         <v>3183</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B41">
         <v>32935</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B44">
         <v>3947</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B45">
         <v>4110</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B48">
         <v>4748</v>
@@ -6360,7 +6360,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B50">
         <v>5196</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B52">
         <v>5246</v>
@@ -6724,7 +6724,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B53">
         <v>5422</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B54">
         <v>5445</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B55">
         <v>5751</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B56">
         <v>5803</v>
@@ -7241,7 +7241,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B57">
         <v>5810</v>
@@ -7364,7 +7364,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B58">
         <v>5814</v>
@@ -11259,7 +11259,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B74">
         <v>1259</v>
@@ -11282,7 +11282,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B75">
         <v>1322</v>
@@ -11305,7 +11305,7 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B76">
         <v>1322</v>
@@ -11328,7 +11328,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B77">
         <v>1322</v>
@@ -11351,7 +11351,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B78">
         <v>1344</v>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B79">
         <v>1344</v>
@@ -11397,7 +11397,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B80">
         <v>1344</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B81">
         <v>1418</v>
@@ -11443,7 +11443,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B82">
         <v>1420</v>
@@ -11466,7 +11466,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B83">
         <v>1429</v>
@@ -11489,7 +11489,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B84">
         <v>1429</v>
@@ -11512,7 +11512,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B85">
         <v>1429</v>
@@ -11535,7 +11535,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B86">
         <v>1429</v>
@@ -11558,7 +11558,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B87">
         <v>1441</v>
@@ -11581,7 +11581,7 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B88">
         <v>1506</v>
@@ -11604,7 +11604,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B89">
         <v>1572</v>
@@ -11627,7 +11627,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B90">
         <v>1572</v>
@@ -11650,7 +11650,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B91">
         <v>1572</v>
@@ -11673,7 +11673,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B92">
         <v>1647</v>
@@ -11696,7 +11696,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B93">
         <v>1647</v>
@@ -11719,7 +11719,7 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B94">
         <v>1664</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B95">
         <v>1905</v>
@@ -11765,7 +11765,7 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B96">
         <v>1920</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B97">
         <v>1920</v>
@@ -11811,7 +11811,7 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B98">
         <v>1924</v>
@@ -11834,7 +11834,7 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B99">
         <v>1960</v>
@@ -11857,7 +11857,7 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B100">
         <v>1969</v>
@@ -11880,7 +11880,7 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B101">
         <v>1969</v>
@@ -11903,7 +11903,7 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B102">
         <v>1969</v>
@@ -11926,7 +11926,7 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B103">
         <v>1970</v>
@@ -11949,7 +11949,7 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B104">
         <v>2150</v>
@@ -11972,7 +11972,7 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B105">
         <v>2150</v>
@@ -11995,7 +11995,7 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B106">
         <v>2420</v>
@@ -12018,7 +12018,7 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B107">
         <v>2680</v>
@@ -12041,7 +12041,7 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B108">
         <v>2680</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B109">
         <v>3183</v>
@@ -12087,7 +12087,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B110">
         <v>3947</v>
@@ -12110,7 +12110,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B111">
         <v>3947</v>
@@ -12133,7 +12133,7 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B112">
         <v>4110</v>
@@ -12156,7 +12156,7 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B113">
         <v>4110</v>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B114">
         <v>4110</v>
@@ -12202,7 +12202,7 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B115">
         <v>4748</v>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B116">
         <v>4748</v>
@@ -12248,7 +12248,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B117">
         <v>4748</v>
@@ -12271,7 +12271,7 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B118">
         <v>5196</v>
@@ -12294,7 +12294,7 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B119">
         <v>5246</v>
@@ -12317,7 +12317,7 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B120">
         <v>5246</v>
@@ -12340,7 +12340,7 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B121">
         <v>5422</v>
@@ -12363,7 +12363,7 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B122">
         <v>5445</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B123">
         <v>5751</v>
@@ -12409,7 +12409,7 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B124">
         <v>5751</v>
@@ -12432,7 +12432,7 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B125">
         <v>5803</v>
@@ -12455,7 +12455,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B126">
         <v>5803</v>
@@ -12478,7 +12478,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B127">
         <v>5803</v>
@@ -12501,7 +12501,7 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B128">
         <v>5810</v>
@@ -12524,7 +12524,7 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B129">
         <v>5810</v>
@@ -12547,7 +12547,7 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B130">
         <v>5814</v>
@@ -12570,7 +12570,7 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B131">
         <v>5814</v>
@@ -12593,7 +12593,7 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B132">
         <v>21829</v>
@@ -12616,7 +12616,7 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B133">
         <v>21829</v>
@@ -12639,7 +12639,7 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B134">
         <v>32935</v>
@@ -12662,7 +12662,7 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B135">
         <v>32935</v>
@@ -12685,7 +12685,7 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B136">
         <v>32935</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B137">
         <v>32935</v>
@@ -12731,7 +12731,7 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B138">
         <v>32935</v>
@@ -12754,7 +12754,7 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B139">
         <v>32935</v>
@@ -12777,7 +12777,7 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B140">
         <v>32935</v>
@@ -12992,7 +12992,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12">
         <v>1259</v>
@@ -13008,7 +13008,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B13">
         <v>1322</v>
@@ -13024,7 +13024,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14">
         <v>1344</v>
@@ -13056,7 +13056,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B16">
         <v>1418</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B17">
         <v>1420</v>
@@ -13088,7 +13088,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18">
         <v>1429</v>
@@ -13104,7 +13104,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B19">
         <v>1506</v>
@@ -13120,7 +13120,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B20">
         <v>1572</v>
@@ -13136,7 +13136,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21">
         <v>1647</v>
@@ -13152,7 +13152,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B22">
         <v>1664</v>
@@ -13168,7 +13168,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B23">
         <v>1905</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B24">
         <v>1920</v>
@@ -13200,7 +13200,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25">
         <v>1924</v>
@@ -13216,7 +13216,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26">
         <v>1960</v>
@@ -13232,7 +13232,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B27">
         <v>1969</v>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B28">
         <v>1970</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31">
         <v>2150</v>
@@ -13312,7 +13312,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B32">
         <v>21829</v>
@@ -13328,7 +13328,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33">
         <v>2680</v>
@@ -13360,7 +13360,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35">
         <v>3183</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B38">
         <v>32935</v>
@@ -13440,7 +13440,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B40">
         <v>3947</v>
@@ -13456,7 +13456,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B41">
         <v>4110</v>
@@ -13504,7 +13504,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B44">
         <v>4748</v>
@@ -13536,7 +13536,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46">
         <v>5196</v>
@@ -13568,7 +13568,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B48">
         <v>5246</v>
@@ -13584,7 +13584,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B49">
         <v>5422</v>
@@ -13600,7 +13600,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B50">
         <v>5445</v>
@@ -13616,7 +13616,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B51">
         <v>5751</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B52">
         <v>5803</v>
@@ -13648,7 +13648,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B53">
         <v>5810</v>
@@ -13664,7 +13664,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B54">
         <v>5814</v>
@@ -14508,7 +14508,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32">
         <v>1259</v>
@@ -14526,7 +14526,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33">
         <v>1259</v>
@@ -14544,7 +14544,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B34">
         <v>1259</v>
@@ -14562,7 +14562,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B35">
         <v>1322</v>
@@ -14580,7 +14580,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B36">
         <v>1322</v>
@@ -14598,7 +14598,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B37">
         <v>1344</v>
@@ -14616,7 +14616,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B38">
         <v>1344</v>
@@ -14706,7 +14706,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B43">
         <v>1418</v>
@@ -14724,7 +14724,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B44">
         <v>1420</v>
@@ -14742,7 +14742,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45">
         <v>1420</v>
@@ -14760,7 +14760,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46">
         <v>1429</v>
@@ -14778,7 +14778,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B47">
         <v>1429</v>
@@ -14796,7 +14796,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B48">
         <v>1429</v>
@@ -14814,7 +14814,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B49">
         <v>1441</v>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50">
         <v>1441</v>
@@ -14850,7 +14850,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B51">
         <v>1441</v>
@@ -14868,7 +14868,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B52">
         <v>1441</v>
@@ -14886,7 +14886,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B53">
         <v>1506</v>
@@ -14904,7 +14904,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54">
         <v>1506</v>
@@ -14922,7 +14922,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B55">
         <v>1572</v>
@@ -14940,7 +14940,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B56">
         <v>1572</v>
@@ -14958,7 +14958,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B57">
         <v>1647</v>
@@ -14976,7 +14976,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B58">
         <v>1647</v>
@@ -14994,7 +14994,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B59">
         <v>1664</v>
@@ -15012,7 +15012,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B60">
         <v>1664</v>
@@ -15030,7 +15030,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B61">
         <v>1664</v>
@@ -15048,7 +15048,7 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B62">
         <v>1664</v>
@@ -15066,7 +15066,7 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B63">
         <v>1905</v>
@@ -15084,7 +15084,7 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B64">
         <v>1905</v>
@@ -15102,7 +15102,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B65">
         <v>1920</v>
@@ -15120,7 +15120,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B66">
         <v>1920</v>
@@ -15138,7 +15138,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B67">
         <v>1924</v>
@@ -15156,7 +15156,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B68">
         <v>1960</v>
@@ -15174,7 +15174,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B69">
         <v>1960</v>
@@ -15192,7 +15192,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B70">
         <v>1960</v>
@@ -15210,7 +15210,7 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B71">
         <v>1960</v>
@@ -15228,7 +15228,7 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B72">
         <v>1969</v>
@@ -15246,7 +15246,7 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B73">
         <v>1969</v>
@@ -15264,7 +15264,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B74">
         <v>1970</v>
@@ -15282,7 +15282,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B75">
         <v>1970</v>
@@ -15354,7 +15354,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B79">
         <v>2150</v>
@@ -15372,7 +15372,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B80">
         <v>2150</v>
@@ -15390,7 +15390,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B81">
         <v>21829</v>
@@ -15408,7 +15408,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B82">
         <v>21829</v>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B83">
         <v>2420</v>
@@ -15444,7 +15444,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B84">
         <v>2420</v>
@@ -15462,7 +15462,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B85">
         <v>2420</v>
@@ -15480,7 +15480,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B86">
         <v>2420</v>
@@ -15498,7 +15498,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B87">
         <v>2680</v>
@@ -15534,7 +15534,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B89">
         <v>3183</v>
@@ -15552,7 +15552,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B90">
         <v>3183</v>
@@ -15570,7 +15570,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B91">
         <v>3183</v>
@@ -15588,7 +15588,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B92">
         <v>3183</v>
@@ -15678,7 +15678,7 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B97">
         <v>32935</v>
@@ -15696,7 +15696,7 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B98">
         <v>32935</v>
@@ -15750,7 +15750,7 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B101">
         <v>3947</v>
@@ -15768,7 +15768,7 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B102">
         <v>3947</v>
@@ -15786,7 +15786,7 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B103">
         <v>3947</v>
@@ -15804,7 +15804,7 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B104">
         <v>3947</v>
@@ -15822,7 +15822,7 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B105">
         <v>4110</v>
@@ -15912,7 +15912,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B110">
         <v>4748</v>
@@ -15930,7 +15930,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B111">
         <v>4748</v>
@@ -15984,7 +15984,7 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B114">
         <v>5196</v>
@@ -16038,7 +16038,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B117">
         <v>5246</v>
@@ -16056,7 +16056,7 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B118">
         <v>5246</v>
@@ -16074,7 +16074,7 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B119">
         <v>5422</v>
@@ -16092,7 +16092,7 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B120">
         <v>5445</v>
@@ -16110,7 +16110,7 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B121">
         <v>5445</v>
@@ -16128,7 +16128,7 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B122">
         <v>5751</v>
@@ -16146,7 +16146,7 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B123">
         <v>5751</v>
@@ -16164,7 +16164,7 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B124">
         <v>5751</v>
@@ -16182,7 +16182,7 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B125">
         <v>5751</v>
@@ -16200,7 +16200,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B126">
         <v>5803</v>
@@ -16218,7 +16218,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B127">
         <v>5803</v>
@@ -16236,7 +16236,7 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B128">
         <v>5810</v>
@@ -16254,7 +16254,7 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B129">
         <v>5814</v>
@@ -17150,7 +17150,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15">
         <v>1259</v>
@@ -17168,7 +17168,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16">
         <v>1259</v>
@@ -17186,7 +17186,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17">
         <v>1322</v>
@@ -17204,7 +17204,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18">
         <v>1344</v>
@@ -17240,7 +17240,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20">
         <v>1418</v>
@@ -17258,7 +17258,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B21">
         <v>1420</v>
@@ -17276,7 +17276,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B22">
         <v>1429</v>
@@ -17294,7 +17294,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23">
         <v>1441</v>
@@ -17312,7 +17312,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B24">
         <v>1506</v>
@@ -17330,7 +17330,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25">
         <v>1572</v>
@@ -17348,7 +17348,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26">
         <v>1647</v>
@@ -17366,7 +17366,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27">
         <v>1664</v>
@@ -17384,7 +17384,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28">
         <v>1905</v>
@@ -17402,7 +17402,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29">
         <v>1905</v>
@@ -17420,7 +17420,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30">
         <v>1920</v>
@@ -17438,7 +17438,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31">
         <v>1924</v>
@@ -17456,7 +17456,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32">
         <v>1924</v>
@@ -17474,7 +17474,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B33">
         <v>1960</v>
@@ -17492,7 +17492,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34">
         <v>1969</v>
@@ -17510,7 +17510,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B35">
         <v>1970</v>
@@ -17528,7 +17528,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B36">
         <v>1970</v>
@@ -17546,7 +17546,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B37">
         <v>1970</v>
@@ -17600,7 +17600,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B40">
         <v>2150</v>
@@ -17618,7 +17618,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B41">
         <v>2150</v>
@@ -17636,7 +17636,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B42">
         <v>2150</v>
@@ -17654,7 +17654,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B43">
         <v>21829</v>
@@ -17672,7 +17672,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44">
         <v>21829</v>
@@ -17690,7 +17690,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B45">
         <v>2420</v>
@@ -17708,7 +17708,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B46">
         <v>2680</v>
@@ -17744,7 +17744,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B48">
         <v>3183</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B51">
         <v>32935</v>
@@ -17816,7 +17816,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B52">
         <v>32935</v>
@@ -17888,7 +17888,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B56">
         <v>3947</v>
@@ -17906,7 +17906,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57">
         <v>4110</v>
@@ -17924,7 +17924,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B58">
         <v>4110</v>
@@ -17978,7 +17978,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B61">
         <v>4748</v>
@@ -18014,7 +18014,7 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B63">
         <v>5196</v>
@@ -18050,7 +18050,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B65">
         <v>5246</v>
@@ -18068,7 +18068,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B66">
         <v>5422</v>
@@ -18086,7 +18086,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B67">
         <v>5445</v>
@@ -18104,7 +18104,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B68">
         <v>5751</v>
@@ -18122,7 +18122,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B69">
         <v>5803</v>
@@ -18140,7 +18140,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B70">
         <v>5810</v>
@@ -18158,7 +18158,7 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B71">
         <v>5814</v>
@@ -23103,7 +23103,7 @@
     </row>
     <row r="207">
       <c r="A207">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B207">
         <v>1259</v>
@@ -23126,7 +23126,7 @@
     </row>
     <row r="208">
       <c r="A208">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B208">
         <v>1259</v>
@@ -23149,7 +23149,7 @@
     </row>
     <row r="209">
       <c r="A209">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B209">
         <v>1259</v>
@@ -23172,7 +23172,7 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B210">
         <v>1259</v>
@@ -23195,7 +23195,7 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B211">
         <v>1259</v>
@@ -23218,7 +23218,7 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B212">
         <v>1259</v>
@@ -23241,7 +23241,7 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B213">
         <v>1259</v>
@@ -23264,7 +23264,7 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B214">
         <v>1259</v>
@@ -23287,7 +23287,7 @@
     </row>
     <row r="215">
       <c r="A215">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B215">
         <v>1259</v>
@@ -23310,7 +23310,7 @@
     </row>
     <row r="216">
       <c r="A216">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B216">
         <v>1259</v>
@@ -23333,7 +23333,7 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B217">
         <v>1259</v>
@@ -23356,7 +23356,7 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B218">
         <v>1259</v>
@@ -23379,7 +23379,7 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B219">
         <v>1259</v>
@@ -23402,7 +23402,7 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B220">
         <v>1259</v>
@@ -23425,7 +23425,7 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B221">
         <v>1259</v>
@@ -23448,7 +23448,7 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B222">
         <v>1259</v>
@@ -23471,7 +23471,7 @@
     </row>
     <row r="223">
       <c r="A223">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B223">
         <v>1322</v>
@@ -23494,7 +23494,7 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B224">
         <v>1322</v>
@@ -23517,7 +23517,7 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B225">
         <v>1322</v>
@@ -23540,7 +23540,7 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B226">
         <v>1322</v>
@@ -23563,7 +23563,7 @@
     </row>
     <row r="227">
       <c r="A227">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B227">
         <v>1322</v>
@@ -23586,7 +23586,7 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B228">
         <v>1322</v>
@@ -23609,7 +23609,7 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B229">
         <v>1418</v>
@@ -23632,7 +23632,7 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B230">
         <v>1418</v>
@@ -23655,7 +23655,7 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B231">
         <v>1420</v>
@@ -23678,7 +23678,7 @@
     </row>
     <row r="232">
       <c r="A232">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B232">
         <v>1420</v>
@@ -23701,7 +23701,7 @@
     </row>
     <row r="233">
       <c r="A233">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B233">
         <v>1420</v>
@@ -23724,7 +23724,7 @@
     </row>
     <row r="234">
       <c r="A234">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B234">
         <v>1420</v>
@@ -23747,7 +23747,7 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B235">
         <v>1420</v>
@@ -23770,7 +23770,7 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B236">
         <v>1420</v>
@@ -23793,7 +23793,7 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B237">
         <v>1429</v>
@@ -23816,7 +23816,7 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B238">
         <v>1429</v>
@@ -23839,7 +23839,7 @@
     </row>
     <row r="239">
       <c r="A239">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B239">
         <v>1429</v>
@@ -23862,7 +23862,7 @@
     </row>
     <row r="240">
       <c r="A240">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B240">
         <v>1429</v>
@@ -23885,7 +23885,7 @@
     </row>
     <row r="241">
       <c r="A241">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B241">
         <v>1429</v>
@@ -23908,7 +23908,7 @@
     </row>
     <row r="242">
       <c r="A242">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B242">
         <v>1429</v>
@@ -23931,7 +23931,7 @@
     </row>
     <row r="243">
       <c r="A243">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B243">
         <v>1429</v>
@@ -23954,7 +23954,7 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B244">
         <v>1429</v>
@@ -23977,7 +23977,7 @@
     </row>
     <row r="245">
       <c r="A245">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B245">
         <v>1429</v>
@@ -24000,7 +24000,7 @@
     </row>
     <row r="246">
       <c r="A246">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B246">
         <v>1429</v>
@@ -24023,7 +24023,7 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B247">
         <v>1429</v>
@@ -24046,7 +24046,7 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B248">
         <v>1429</v>
@@ -24069,7 +24069,7 @@
     </row>
     <row r="249">
       <c r="A249">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B249">
         <v>1429</v>
@@ -24092,7 +24092,7 @@
     </row>
     <row r="250">
       <c r="A250">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B250">
         <v>1441</v>
@@ -24115,7 +24115,7 @@
     </row>
     <row r="251">
       <c r="A251">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B251">
         <v>1441</v>
@@ -24138,7 +24138,7 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B252">
         <v>1441</v>
@@ -24161,7 +24161,7 @@
     </row>
     <row r="253">
       <c r="A253">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B253">
         <v>1441</v>
@@ -24184,7 +24184,7 @@
     </row>
     <row r="254">
       <c r="A254">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B254">
         <v>1572</v>
@@ -24207,7 +24207,7 @@
     </row>
     <row r="255">
       <c r="A255">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B255">
         <v>1572</v>
@@ -24230,7 +24230,7 @@
     </row>
     <row r="256">
       <c r="A256">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B256">
         <v>1572</v>
@@ -24253,7 +24253,7 @@
     </row>
     <row r="257">
       <c r="A257">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B257">
         <v>1647</v>
@@ -24276,7 +24276,7 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B258">
         <v>1647</v>
@@ -24299,7 +24299,7 @@
     </row>
     <row r="259">
       <c r="A259">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B259">
         <v>1647</v>
@@ -24322,7 +24322,7 @@
     </row>
     <row r="260">
       <c r="A260">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B260">
         <v>1647</v>
@@ -24345,7 +24345,7 @@
     </row>
     <row r="261">
       <c r="A261">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B261">
         <v>1647</v>
@@ -24368,7 +24368,7 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B262">
         <v>1664</v>
@@ -24391,7 +24391,7 @@
     </row>
     <row r="263">
       <c r="A263">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B263">
         <v>1664</v>
@@ -24414,7 +24414,7 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B264">
         <v>1664</v>
@@ -24437,7 +24437,7 @@
     </row>
     <row r="265">
       <c r="A265">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B265">
         <v>1664</v>
@@ -24460,7 +24460,7 @@
     </row>
     <row r="266">
       <c r="A266">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B266">
         <v>1905</v>
@@ -24483,7 +24483,7 @@
     </row>
     <row r="267">
       <c r="A267">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B267">
         <v>1920</v>
@@ -24506,7 +24506,7 @@
     </row>
     <row r="268">
       <c r="A268">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B268">
         <v>1920</v>
@@ -24529,7 +24529,7 @@
     </row>
     <row r="269">
       <c r="A269">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B269">
         <v>1920</v>
@@ -24552,7 +24552,7 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B270">
         <v>1920</v>
@@ -24575,7 +24575,7 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B271">
         <v>1920</v>
@@ -24598,7 +24598,7 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B272">
         <v>1920</v>
@@ -24621,7 +24621,7 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B273">
         <v>1920</v>
@@ -24644,7 +24644,7 @@
     </row>
     <row r="274">
       <c r="A274">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B274">
         <v>1920</v>
@@ -24667,7 +24667,7 @@
     </row>
     <row r="275">
       <c r="A275">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B275">
         <v>1920</v>
@@ -24690,7 +24690,7 @@
     </row>
     <row r="276">
       <c r="A276">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B276">
         <v>1920</v>
@@ -24713,7 +24713,7 @@
     </row>
     <row r="277">
       <c r="A277">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B277">
         <v>1920</v>
@@ -24736,7 +24736,7 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B278">
         <v>1920</v>
@@ -24759,7 +24759,7 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B279">
         <v>1920</v>
@@ -24782,7 +24782,7 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B280">
         <v>1920</v>
@@ -24805,7 +24805,7 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B281">
         <v>1920</v>
@@ -24828,7 +24828,7 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B282">
         <v>1920</v>
@@ -24851,7 +24851,7 @@
     </row>
     <row r="283">
       <c r="A283">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B283">
         <v>1920</v>
@@ -24874,7 +24874,7 @@
     </row>
     <row r="284">
       <c r="A284">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B284">
         <v>1920</v>
@@ -24897,7 +24897,7 @@
     </row>
     <row r="285">
       <c r="A285">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B285">
         <v>1920</v>
@@ -24920,7 +24920,7 @@
     </row>
     <row r="286">
       <c r="A286">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B286">
         <v>1924</v>
@@ -24943,7 +24943,7 @@
     </row>
     <row r="287">
       <c r="A287">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B287">
         <v>1924</v>
@@ -24966,7 +24966,7 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B288">
         <v>1924</v>
@@ -24989,7 +24989,7 @@
     </row>
     <row r="289">
       <c r="A289">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B289">
         <v>1924</v>
@@ -25012,7 +25012,7 @@
     </row>
     <row r="290">
       <c r="A290">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B290">
         <v>1924</v>
@@ -25035,7 +25035,7 @@
     </row>
     <row r="291">
       <c r="A291">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B291">
         <v>1924</v>
@@ -25058,7 +25058,7 @@
     </row>
     <row r="292">
       <c r="A292">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B292">
         <v>1924</v>
@@ -25081,7 +25081,7 @@
     </row>
     <row r="293">
       <c r="A293">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B293">
         <v>1924</v>
@@ -25104,7 +25104,7 @@
     </row>
     <row r="294">
       <c r="A294">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B294">
         <v>1960</v>
@@ -25127,7 +25127,7 @@
     </row>
     <row r="295">
       <c r="A295">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B295">
         <v>1969</v>
@@ -25150,7 +25150,7 @@
     </row>
     <row r="296">
       <c r="A296">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B296">
         <v>1969</v>
@@ -25173,7 +25173,7 @@
     </row>
     <row r="297">
       <c r="A297">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B297">
         <v>1969</v>
@@ -25196,7 +25196,7 @@
     </row>
     <row r="298">
       <c r="A298">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B298">
         <v>1970</v>
@@ -25219,7 +25219,7 @@
     </row>
     <row r="299">
       <c r="A299">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B299">
         <v>1970</v>
@@ -25242,7 +25242,7 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B300">
         <v>1970</v>
@@ -25265,7 +25265,7 @@
     </row>
     <row r="301">
       <c r="A301">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B301">
         <v>2150</v>
@@ -25288,7 +25288,7 @@
     </row>
     <row r="302">
       <c r="A302">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B302">
         <v>2150</v>
@@ -25311,7 +25311,7 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B303">
         <v>2150</v>
@@ -25334,7 +25334,7 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B304">
         <v>2150</v>
@@ -25357,7 +25357,7 @@
     </row>
     <row r="305">
       <c r="A305">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B305">
         <v>2150</v>
@@ -25380,7 +25380,7 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B306">
         <v>2150</v>
@@ -25403,7 +25403,7 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B307">
         <v>2150</v>
@@ -25426,7 +25426,7 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B308">
         <v>2150</v>
@@ -25449,7 +25449,7 @@
     </row>
     <row r="309">
       <c r="A309">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B309">
         <v>2150</v>
@@ -25472,7 +25472,7 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B310">
         <v>2150</v>
@@ -25495,7 +25495,7 @@
     </row>
     <row r="311">
       <c r="A311">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B311">
         <v>2150</v>
@@ -25518,7 +25518,7 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B312">
         <v>2150</v>
@@ -25541,7 +25541,7 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B313">
         <v>2420</v>
@@ -25564,7 +25564,7 @@
     </row>
     <row r="314">
       <c r="A314">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B314">
         <v>2420</v>
@@ -25587,7 +25587,7 @@
     </row>
     <row r="315">
       <c r="A315">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B315">
         <v>2420</v>
@@ -25610,7 +25610,7 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B316">
         <v>2420</v>
@@ -25633,7 +25633,7 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B317">
         <v>2420</v>
@@ -25656,7 +25656,7 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B318">
         <v>2420</v>
@@ -25679,7 +25679,7 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B319">
         <v>2420</v>
@@ -25702,7 +25702,7 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B320">
         <v>2420</v>
@@ -25725,7 +25725,7 @@
     </row>
     <row r="321">
       <c r="A321">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B321">
         <v>2420</v>
@@ -25748,7 +25748,7 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B322">
         <v>2420</v>
@@ -25771,7 +25771,7 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B323">
         <v>2420</v>
@@ -25794,7 +25794,7 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B324">
         <v>2420</v>
@@ -25817,7 +25817,7 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B325">
         <v>2420</v>
@@ -25840,7 +25840,7 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B326">
         <v>2680</v>
@@ -25863,7 +25863,7 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B327">
         <v>2680</v>
@@ -25886,7 +25886,7 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B328">
         <v>4110</v>
@@ -25909,7 +25909,7 @@
     </row>
     <row r="329">
       <c r="A329">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B329">
         <v>4110</v>
@@ -25932,7 +25932,7 @@
     </row>
     <row r="330">
       <c r="A330">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B330">
         <v>4110</v>
@@ -25955,7 +25955,7 @@
     </row>
     <row r="331">
       <c r="A331">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B331">
         <v>4110</v>
@@ -25978,7 +25978,7 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B332">
         <v>4748</v>
@@ -26001,7 +26001,7 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B333">
         <v>4748</v>
@@ -26024,7 +26024,7 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B334">
         <v>4748</v>
@@ -26047,7 +26047,7 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B335">
         <v>4748</v>
@@ -26070,7 +26070,7 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B336">
         <v>4748</v>
@@ -26093,7 +26093,7 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B337">
         <v>4748</v>
@@ -26116,7 +26116,7 @@
     </row>
     <row r="338">
       <c r="A338">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B338">
         <v>4748</v>
@@ -26139,7 +26139,7 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B339">
         <v>4748</v>
@@ -26162,7 +26162,7 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B340">
         <v>4748</v>
@@ -26185,7 +26185,7 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B341">
         <v>5196</v>
@@ -26208,7 +26208,7 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B342">
         <v>5246</v>
@@ -26226,7 +26226,7 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B343">
         <v>5246</v>
@@ -26244,7 +26244,7 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B344">
         <v>5246</v>
@@ -26262,7 +26262,7 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B345">
         <v>5246</v>
@@ -26280,7 +26280,7 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B346">
         <v>5422</v>
@@ -26303,7 +26303,7 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B347">
         <v>5803</v>
@@ -26326,7 +26326,7 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B348">
         <v>5803</v>
@@ -26349,7 +26349,7 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B349">
         <v>5803</v>
@@ -26372,7 +26372,7 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B350">
         <v>5803</v>
@@ -26395,7 +26395,7 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B351">
         <v>5810</v>
@@ -26418,7 +26418,7 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B352">
         <v>5810</v>
@@ -26441,7 +26441,7 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B353">
         <v>5810</v>
@@ -26464,7 +26464,7 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B354">
         <v>5810</v>
@@ -26487,7 +26487,7 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B355">
         <v>5810</v>
@@ -26510,7 +26510,7 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B356">
         <v>5810</v>
@@ -26533,7 +26533,7 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B357">
         <v>5810</v>
@@ -26556,7 +26556,7 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B358">
         <v>5810</v>
@@ -26579,7 +26579,7 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B359">
         <v>5814</v>
@@ -26602,7 +26602,7 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B360">
         <v>5814</v>
@@ -26625,7 +26625,7 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B361">
         <v>5814</v>
@@ -26648,7 +26648,7 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B362">
         <v>5814</v>
@@ -26671,7 +26671,7 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B363">
         <v>32935</v>
@@ -26689,7 +26689,7 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B364">
         <v>32935</v>
@@ -26707,7 +26707,7 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B365">
         <v>32935</v>
@@ -26725,7 +26725,7 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B366">
         <v>32935</v>
@@ -26743,7 +26743,7 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B367">
         <v>32935</v>
@@ -26761,7 +26761,7 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B368">
         <v>32935</v>
@@ -26779,7 +26779,7 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B369">
         <v>32935</v>
@@ -26797,7 +26797,7 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B370">
         <v>32935</v>
@@ -26815,7 +26815,7 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B371">
         <v>32935</v>
@@ -26833,7 +26833,7 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B372">
         <v>32935</v>
@@ -26851,7 +26851,7 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B373">
         <v>32935</v>
@@ -26869,7 +26869,7 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B374">
         <v>32935</v>
@@ -26887,7 +26887,7 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B375">
         <v>32935</v>
@@ -26905,7 +26905,7 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B376">
         <v>32935</v>
@@ -26923,7 +26923,7 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B377">
         <v>32935</v>
@@ -26941,7 +26941,7 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B378">
         <v>32935</v>
@@ -26959,7 +26959,7 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B379">
         <v>32935</v>
@@ -26977,7 +26977,7 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B380">
         <v>32935</v>
@@ -26995,7 +26995,7 @@
     </row>
     <row r="381">
       <c r="A381">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B381">
         <v>32935</v>
@@ -27013,7 +27013,7 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B382">
         <v>32935</v>
@@ -27031,7 +27031,7 @@
     </row>
     <row r="383">
       <c r="A383">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B383">
         <v>32935</v>
@@ -27049,7 +27049,7 @@
     </row>
     <row r="384">
       <c r="A384">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B384">
         <v>32935</v>
@@ -27067,7 +27067,7 @@
     </row>
     <row r="385">
       <c r="A385">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B385">
         <v>32935</v>
@@ -27085,7 +27085,7 @@
     </row>
     <row r="386">
       <c r="A386">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B386">
         <v>32935</v>
@@ -27103,7 +27103,7 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B387">
         <v>32935</v>
@@ -27121,7 +27121,7 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B388">
         <v>32935</v>
@@ -27139,7 +27139,7 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B389">
         <v>32935</v>
@@ -27157,7 +27157,7 @@
     </row>
     <row r="390">
       <c r="A390">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B390">
         <v>32935</v>
@@ -27175,7 +27175,7 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B391">
         <v>32935</v>
@@ -27193,7 +27193,7 @@
     </row>
     <row r="392">
       <c r="A392">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B392">
         <v>32935</v>
@@ -27211,7 +27211,7 @@
     </row>
     <row r="393">
       <c r="A393">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B393">
         <v>32935</v>
@@ -27229,7 +27229,7 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B394">
         <v>32935</v>
@@ -27247,7 +27247,7 @@
     </row>
     <row r="395">
       <c r="A395">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B395">
         <v>32935</v>
@@ -27265,7 +27265,7 @@
     </row>
     <row r="396">
       <c r="A396">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B396">
         <v>32935</v>
@@ -27283,7 +27283,7 @@
     </row>
     <row r="397">
       <c r="A397">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B397">
         <v>32935</v>
@@ -27301,7 +27301,7 @@
     </row>
     <row r="398">
       <c r="A398">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B398">
         <v>32935</v>
@@ -27319,7 +27319,7 @@
     </row>
     <row r="399">
       <c r="A399">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B399">
         <v>32935</v>
@@ -27337,7 +27337,7 @@
     </row>
     <row r="400">
       <c r="A400">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B400">
         <v>32935</v>
@@ -27355,7 +27355,7 @@
     </row>
     <row r="401">
       <c r="A401">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B401">
         <v>32935</v>
@@ -27373,7 +27373,7 @@
     </row>
     <row r="402">
       <c r="A402">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B402">
         <v>32935</v>
@@ -27391,7 +27391,7 @@
     </row>
     <row r="403">
       <c r="A403">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B403">
         <v>32935</v>
@@ -27409,7 +27409,7 @@
     </row>
     <row r="404">
       <c r="A404">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B404">
         <v>32935</v>
@@ -27427,7 +27427,7 @@
     </row>
     <row r="405">
       <c r="A405">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B405">
         <v>32935</v>
@@ -27445,7 +27445,7 @@
     </row>
     <row r="406">
       <c r="A406">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B406">
         <v>32935</v>
@@ -27463,7 +27463,7 @@
     </row>
     <row r="407">
       <c r="A407">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B407">
         <v>32935</v>
@@ -27481,7 +27481,7 @@
     </row>
     <row r="408">
       <c r="A408">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B408">
         <v>32935</v>
@@ -27499,7 +27499,7 @@
     </row>
     <row r="409">
       <c r="A409">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B409">
         <v>32935</v>
@@ -27517,7 +27517,7 @@
     </row>
     <row r="410">
       <c r="A410">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B410">
         <v>32935</v>
@@ -27535,7 +27535,7 @@
     </row>
     <row r="411">
       <c r="A411">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B411">
         <v>32935</v>
@@ -27553,7 +27553,7 @@
     </row>
     <row r="412">
       <c r="A412">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B412">
         <v>32935</v>
@@ -27571,7 +27571,7 @@
     </row>
     <row r="413">
       <c r="A413">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B413">
         <v>32935</v>
@@ -27589,7 +27589,7 @@
     </row>
     <row r="414">
       <c r="A414">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B414">
         <v>32935</v>
@@ -27607,7 +27607,7 @@
     </row>
     <row r="415">
       <c r="A415">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B415">
         <v>32935</v>
@@ -27625,7 +27625,7 @@
     </row>
     <row r="416">
       <c r="A416">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B416">
         <v>32935</v>
@@ -27643,7 +27643,7 @@
     </row>
     <row r="417">
       <c r="A417">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B417">
         <v>32935</v>
@@ -27661,7 +27661,7 @@
     </row>
     <row r="418">
       <c r="A418">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B418">
         <v>32935</v>
@@ -27679,7 +27679,7 @@
     </row>
     <row r="419">
       <c r="A419">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B419">
         <v>32935</v>
@@ -27697,7 +27697,7 @@
     </row>
     <row r="420">
       <c r="A420">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B420">
         <v>32935</v>
@@ -27715,7 +27715,7 @@
     </row>
     <row r="421">
       <c r="A421">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B421">
         <v>32935</v>
@@ -27733,7 +27733,7 @@
     </row>
     <row r="422">
       <c r="A422">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B422">
         <v>32935</v>
@@ -27751,7 +27751,7 @@
     </row>
     <row r="423">
       <c r="A423">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B423">
         <v>32935</v>
@@ -27769,7 +27769,7 @@
     </row>
     <row r="424">
       <c r="A424">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B424">
         <v>32935</v>
@@ -27787,7 +27787,7 @@
     </row>
     <row r="425">
       <c r="A425">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B425">
         <v>32935</v>
@@ -27805,7 +27805,7 @@
     </row>
     <row r="426">
       <c r="A426">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B426">
         <v>32935</v>
@@ -27823,7 +27823,7 @@
     </row>
     <row r="427">
       <c r="A427">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B427">
         <v>32935</v>
@@ -27841,7 +27841,7 @@
     </row>
     <row r="428">
       <c r="A428">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B428">
         <v>32935</v>
@@ -27859,7 +27859,7 @@
     </row>
     <row r="429">
       <c r="A429">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B429">
         <v>32935</v>
@@ -27877,7 +27877,7 @@
     </row>
     <row r="430">
       <c r="A430">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B430">
         <v>32935</v>
@@ -27895,7 +27895,7 @@
     </row>
     <row r="431">
       <c r="A431">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B431">
         <v>32935</v>
@@ -27913,7 +27913,7 @@
     </row>
     <row r="432">
       <c r="A432">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B432">
         <v>32935</v>
@@ -27931,7 +27931,7 @@
     </row>
     <row r="433">
       <c r="A433">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B433">
         <v>32935</v>
@@ -27949,7 +27949,7 @@
     </row>
     <row r="434">
       <c r="A434">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B434">
         <v>32935</v>
